--- a/docs/xlsx/jobs-2026-09-15.xlsx
+++ b/docs/xlsx/jobs-2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="588">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1753 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Central Klickitat Conservation District</t>
+  </si>
+  <si>
+    <t>Goldendale, WA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$20 - $28 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-administrative-assistant-goldendale-washington/8795971887</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Natural Resource Policy</t>
+  </si>
+  <si>
+    <t>University of Montana</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>Commensurate</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-of-natural-resource-policy-missoula-montana/7387158631</t>
+  </si>
+  <si>
+    <t>Assistant/Associate Professor in Social Science &amp; Sustainability</t>
+  </si>
+  <si>
+    <t>Virginia Tech</t>
+  </si>
+  <si>
+    <t>Blacksburg, VA</t>
+  </si>
+  <si>
+    <t>$85,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistantassociate-professor-in-social-science--sustainability-blacksburg-virginia/5727650168</t>
+  </si>
+  <si>
+    <t>Biologist/Environmental Scientist</t>
+  </si>
+  <si>
+    <t>Nexus Environmental Consultants, Inc.</t>
+  </si>
+  <si>
+    <t>Elko, NV</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$55,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biologistenvironmental-scientist-elko-nevada/2330250122</t>
+  </si>
+  <si>
+    <t>Botanist/Vegetation Specialist</t>
+  </si>
+  <si>
+    <t>Elko or Reno, NV</t>
+  </si>
+  <si>
+    <t>$50,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botanistvegetation-specialist-elko-or-reno-nevada/3914031450</t>
+  </si>
+  <si>
+    <t>Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 (but compensation may range between $40,000 and $44,450 depending on location).</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-campaign-associate-washington-dc/1316968478</t>
+  </si>
+  <si>
+    <t>Consumer Advocacy Associate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-consumer-advocacy-associate-washington-dc/4315455297</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-consumer-advocacy-associate-portland-oregon/8642563127</t>
+  </si>
+  <si>
+    <t>Coös County Senior Educator</t>
+  </si>
+  <si>
+    <t>Appalachian Mountain Club</t>
+  </si>
+  <si>
+    <t>Gorham, NH</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cos-county-senior-educator-gorham-new-hampshire/6538846989</t>
+  </si>
+  <si>
+    <t>Deputy Director (Deputy/Chief 6)</t>
+  </si>
+  <si>
+    <t>Oregon Department of Environmental Quality</t>
+  </si>
+  <si>
+    <t>$11,429 - $17,704 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-deputychief-6-portland-oregon/4844320302</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>Dodge Nature Center</t>
+  </si>
+  <si>
+    <t>West St. Paul, MN</t>
+  </si>
+  <si>
+    <t>$85,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-advancement-west-st-paul-minnesota/1564630169</t>
+  </si>
+  <si>
+    <t>Director of Restoration</t>
+  </si>
+  <si>
+    <t>Anne Arundel Watershed Stewards Academy</t>
+  </si>
+  <si>
+    <t>Crownsville, MD</t>
+  </si>
+  <si>
+    <t>$75,000 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-restoration-crownsville-maryland/1244330833</t>
+  </si>
+  <si>
+    <t>District Forester (Oregon Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>$65,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-oregon-forestry-district-eugene-oregon/4869729698</t>
+  </si>
+  <si>
+    <t>Environmental Organizer</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>The target annual compensation range for this position is $40,000 - $44,450 and depends on location, education and experience.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-los-angeles-california/7228722411</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-boston-massachusetts/9413404475</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-portland-oregon/1937583636</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-organizer-san-francisco-california/8653832362</t>
+  </si>
+  <si>
+    <t>ESA Section 7 Senior Analyst</t>
+  </si>
+  <si>
+    <t>Ocean Associates Inc.</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$37 - $40 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-esa-section-7-senior-analyst-remote-remote/9591819990</t>
+  </si>
+  <si>
+    <t>Evaluation &amp; Trials Coordinator</t>
+  </si>
+  <si>
+    <t>Seed Savers Exchange</t>
+  </si>
+  <si>
+    <t>Decorah, IA</t>
+  </si>
+  <si>
+    <t>$19 per hour</t>
+  </si>
+  <si>
+    <t>botany</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-evaluation--trials-coordinator-decorah-iowa/6886649472</t>
+  </si>
+  <si>
+    <t>Field Ecologist</t>
+  </si>
+  <si>
+    <t>CC Environment &amp; Planning</t>
+  </si>
+  <si>
+    <t>Batavia, NY</t>
+  </si>
+  <si>
+    <t>$26 - $29 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-ecologist-batavia-new-york/7991521919</t>
+  </si>
+  <si>
+    <t>Field Operator</t>
+  </si>
+  <si>
+    <t>Eagle River Water &amp; Sanitation District</t>
+  </si>
+  <si>
+    <t>Vail, CO</t>
+  </si>
+  <si>
+    <t>$27.74 - $52.05 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-operator-vail-colorado/8113232490</t>
+  </si>
+  <si>
+    <t>Field Technician</t>
+  </si>
+  <si>
+    <t>CC Environment and Planning</t>
+  </si>
+  <si>
+    <t>$22 - $25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-technician-batavia-new-york/5168184259</t>
+  </si>
+  <si>
+    <t>Institutional Giving Officer</t>
+  </si>
+  <si>
+    <t>Western Landowners Alliance</t>
+  </si>
+  <si>
+    <t>Dener, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-institutional-giving-officer-dener-colorado/7105361680</t>
+  </si>
+  <si>
+    <t>INTERNSHIP - Environmental Science Research</t>
+  </si>
+  <si>
+    <t>The Conservancy of Southwest Florida</t>
+  </si>
+  <si>
+    <t>Naples, FL</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>$150 per week</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-internship---environmental-science-research-naples-florida/9544587619</t>
+  </si>
+  <si>
+    <t>Montana AgCorps Member</t>
+  </si>
+  <si>
+    <t>Montana AgCorps</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$23,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-montana-agcorps-member-helena-montana/7681216641</t>
+  </si>
+  <si>
+    <t>Nature Preschool Teacher</t>
+  </si>
+  <si>
+    <t>Chippewa Nature Center</t>
+  </si>
+  <si>
+    <t>Midland, MI</t>
+  </si>
+  <si>
+    <t>$27,000 - $36,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-nature-preschool-teacher-midland---mi-michigan/3397649989</t>
+  </si>
+  <si>
+    <t>New York Program Director</t>
+  </si>
+  <si>
+    <t>Land Trust Alliance</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>$110,000 - $130,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-new-york-program-director-new-york-new-york/6901574593</t>
+  </si>
+  <si>
+    <t>Planning Team Leader - Open Space</t>
+  </si>
+  <si>
+    <t>Santa Fe County</t>
+  </si>
+  <si>
+    <t>Santa Fe, NM</t>
+  </si>
+  <si>
+    <t>$69,035 - $82,825 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-planning-team-leader---open-space-santa-fe-new-mexico/1246303505</t>
+  </si>
+  <si>
+    <t>Public Interest State Advocate</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation range for someone with 2-8 years of relevant experience is $41,750-$60,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-interest-state-advocate-austin-texas/5768224072</t>
+  </si>
+  <si>
+    <t>Quantitative Analysis, Predation Modeling, Data Synthesis Support</t>
+  </si>
+  <si>
+    <t>Seattle or Pasco, WA</t>
+  </si>
+  <si>
+    <t>$45 - $50 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-quantitative-analysis-predation-modeling-data-synthesis-support-seattle-or-pasco-washington/3974959947</t>
+  </si>
+  <si>
+    <t>Racine Zoo AmeriCorps Volunteer</t>
+  </si>
+  <si>
+    <t>Racine Zoo AmeriCorps Program</t>
+  </si>
+  <si>
+    <t>Racine, WI</t>
+  </si>
+  <si>
+    <t>$1,005 per month</t>
+  </si>
+  <si>
+    <t>environmental-education-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-racine-zoo-americorps-volunteer-racine-wisconsin/6406446229</t>
+  </si>
+  <si>
+    <t>Resource Conservation Planner or Technician/Planner Apprentice</t>
+  </si>
+  <si>
+    <t>South Yakima Conservation District</t>
+  </si>
+  <si>
+    <t>Zillah, WA</t>
+  </si>
+  <si>
+    <t>$3,400 - $5,400 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-resource-conservation-planner-or-technicianplanner-apprentice-zillah-washington/6433795101</t>
+  </si>
+  <si>
+    <t>Restoration Project Manager</t>
+  </si>
+  <si>
+    <t>Share hourly rate</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-project-manager-crownsville-maryland/7726173456</t>
+  </si>
+  <si>
+    <t>Seasonal Biologist/Environmental Scientist</t>
+  </si>
+  <si>
+    <t>$23 - $30 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-biologistenvironmental-scientist-elko-or-reno-nevada/9389209494</t>
+  </si>
+  <si>
+    <t>Seasonal Botanist/Vegetation Specialist</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-botanistvegetation-specialist-elko-or-reno-nevada/3317643758</t>
+  </si>
+  <si>
+    <t>Seasonal Wildlife Caretaker</t>
+  </si>
+  <si>
+    <t>Wildlife Center of Long Island</t>
+  </si>
+  <si>
+    <t>Huntington, NY</t>
+  </si>
+  <si>
+    <t>$20 - $23 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-seasonal-wildlife-caretaker-huntington-new-york/4176629778</t>
+  </si>
+  <si>
+    <t>Smokebusters Crew Supervisor</t>
+  </si>
+  <si>
+    <t>State of Wyoming</t>
+  </si>
+  <si>
+    <t>Cheyenne, WY</t>
+  </si>
+  <si>
+    <t>$29.76 - $33.06 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-smokebusters-crew-supervisor-cheyenne-wyoming/2299548212</t>
+  </si>
+  <si>
+    <t>Statistician</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-statistician-seattle-washington/2080792978</t>
+  </si>
+  <si>
+    <t>Tree Ambassador</t>
+  </si>
+  <si>
+    <t>City of Austin</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tree-ambassador-austin-texas/4893694627</t>
+  </si>
+  <si>
+    <t>Wildlife Caretaker</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-caretaker-huntington-new-york/8326363376</t>
+  </si>
+  <si>
+    <t>Winter Sustainability Associate</t>
+  </si>
+  <si>
+    <t>Bogus Basin Recreational Association</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-winter-sustainability-associate-boise-idaho/7217454191</t>
+  </si>
+  <si>
+    <t>Zero Waste Campaign Associate</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-zero-waste-campaign-associate-los-angeles-california/8621720650</t>
+  </si>
+  <si>
+    <t>Information Systems &amp; Technology Intern</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, California, United States</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/information-systems-technology-intern-3/</t>
+  </si>
+  <si>
+    <t>Adult Protective Services Case Manager</t>
+  </si>
+  <si>
+    <t>FOCUS Hispanic Center for Community Development, Inc</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5b0174e2afd4b49b21be5eeb140bddb-adult-protective-services-case-manager-focus-hispanic-center-for-community-development-inc-newark</t>
+  </si>
+  <si>
+    <t>Advocacy and Outreach Senior Coordinator</t>
+  </si>
+  <si>
+    <t>California Native Plant Society (CNPS)</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>USD 31.51 - 33.96/hour</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b38e4e19c9124f3eb5266146b17ccade-advocacy-and-outreach-senior-coordinator-california-native-plant-society-cnps-sacramento</t>
+  </si>
+  <si>
+    <t>After School Academic Mentor</t>
+  </si>
+  <si>
+    <t>Oakland Kids First</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b02b8873e1704e16abd16dca4624f3ba-after-school-academic-mentor-oakland-kids-first-oakland</t>
+  </si>
+  <si>
+    <t>After School Program Assistant</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c660cad7b64b4b58acf44a3d8cff7ce6-after-school-program-assistant-oakland-kids-first-oakland</t>
+  </si>
+  <si>
+    <t>Assistant Educator [Federal Way]</t>
+  </si>
+  <si>
+    <t>Geeking Out Kids of Color (GOKiC)</t>
+  </si>
+  <si>
+    <t>Federal Way, Washington</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94cc17d973d64f2996fcfec9c4cc0abd-assistant-educator-federal-way-geeking-out-kids-of-color-gokic-federal-way</t>
+  </si>
+  <si>
+    <t>Associate Development Officer, Leadership Giving</t>
+  </si>
+  <si>
+    <t>Partners In Health</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70040.00 - 74160.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b78f4a146d56470d8afc1e82a6c51b03-associate-development-officer-leadership-giving-partners-in-health-boston</t>
+  </si>
+  <si>
+    <t>Associate Director for Individual Giving, Development</t>
+  </si>
+  <si>
+    <t>American Library Association</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1dfd0bb5a74f4bd59c042850d43f8f6b-associate-director-for-individual-giving-development-american-library-association-chicago</t>
+  </si>
+  <si>
+    <t>Business Analyst / Strategy &amp; Operations - Director's Associate - Chennai Residents Only</t>
+  </si>
+  <si>
+    <t>Empower Tamizhagam</t>
+  </si>
+  <si>
+    <t>Chennai, Tamil Nadu, IN</t>
+  </si>
+  <si>
+    <t>INR 30000.00 - 50000.00/month</t>
+  </si>
+  <si>
+    <t>Economic Development, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac4827c852d544ad80069eb643a538d4-business-analyst-strategy-operations-directors-associate-chennai-residents-only-empower-tamizhagam-chennai</t>
+  </si>
+  <si>
+    <t>Business and Procurement Manager</t>
+  </si>
+  <si>
+    <t>Encore Community Services</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 120000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e221929c66224cf1bb85d25cccf03b3a-business-and-procurement-manager-encore-community-services-new-york</t>
+  </si>
+  <si>
+    <t>Business Partner, Human Resources</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 102900.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6f7b0aca61d499399a7e06cb38900aa-business-partner-human-resources-tsne-boston</t>
+  </si>
+  <si>
+    <t>Captadores/as de Fondos en vía pública para CABA + Zona Oeste</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Community Development, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/035edc34fc9c4c9e8b354f35a707c867-captadoresas-de-fondos-en-via-publica-para-caba-zona-oeste-aldeas-infantiles-sos-argentina-buenos-aires</t>
+  </si>
+  <si>
+    <t>Chief Advancement Officer</t>
+  </si>
+  <si>
+    <t>Our Children's Trust</t>
+  </si>
+  <si>
+    <t>USD 171850.00 - 198170.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb3de818de914fab8c6a9035c3317735-chief-advancement-officer-our-childrens-trust-eugene</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>LA Promise Fund</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a1f16cee08e4b04bf2370a53ed37f4b-chief-financial-officer-la-promise-fund-los-angeles</t>
+  </si>
+  <si>
+    <t>Client Services Case Manager</t>
+  </si>
+  <si>
+    <t>Medicare Rights Center</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b5ac982239f547e0b48af60ebc141b14-client-services-case-manager-medicare-rights-center-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Social Media Manager</t>
+  </si>
+  <si>
+    <t>Massachusetts Chapter of the American Academy of Pediatrics</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bee59221964f461b99c06cf859173ddd-communications-and-social-media-manager-massachusetts-chapter-of-the-american-academy-of-pediatrics-newton</t>
+  </si>
+  <si>
+    <t>Communications Coordinator</t>
+  </si>
+  <si>
+    <t>U.S. Grains &amp; BioProducts Council</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e9c133a390d40f3b1f48020e4f7b23d-communications-coordinator-us-grains-bioproducts-council-washington</t>
+  </si>
+  <si>
+    <t>Community Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Civic Works</t>
+  </si>
+  <si>
+    <t>Baltimore, MD</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6da16fb0f1014f03902621df7a742a4e-community-outreach-coordinator-civic-works-baltimore</t>
+  </si>
+  <si>
+    <t>Compliance Lead</t>
+  </si>
+  <si>
+    <t>Natural Resource Governance Institute</t>
+  </si>
+  <si>
+    <t>Economic Development, International Relations, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a526b40a42344b892acbce88209226d-compliance-lead-natural-resource-governance-institute-new-york</t>
+  </si>
+  <si>
+    <t>Consulting Immigration / Asylum Attorney</t>
+  </si>
+  <si>
+    <t>RIF Asylum Support</t>
+  </si>
+  <si>
+    <t>USD 150.00 - 150.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6dfc252436e045b39ddda7865da6c557-consulting-immigration-asylum-attorney-rif-asylum-support-new-york</t>
+  </si>
+  <si>
+    <t>Controller</t>
+  </si>
+  <si>
+    <t>JCC Association</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/df242d40134e4aaba3d9119b265d2dbd-controller-jcc-association-new-york</t>
+  </si>
+  <si>
+    <t>Coordinador SR de Desarrollo de fondos/perfil comercial</t>
+  </si>
+  <si>
+    <t>Banco de Alimentos</t>
+  </si>
+  <si>
+    <t>Benavidez, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bd1b28f8f8484d459df00ca1581281cc-coordinador-sr-de-desarrollo-de-fondosperfil-comercial-banco-de-alimentos-benavidez</t>
+  </si>
+  <si>
+    <t>COORDINADOR/A DE OPERACIONES TERRITORIALES - NORTE DE SALTA</t>
+  </si>
+  <si>
+    <t>Asociación Civil Pata Pila</t>
+  </si>
+  <si>
+    <t>Tartagal, Salta, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ca9f595d36074f86b2dc3e90622f7e5b-coordinadora-de-operaciones-territoriales-norte-de-salta-asociacion-civil-pata-pila-tartagal</t>
+  </si>
+  <si>
+    <t>Demand Generation Campaigns Strategist</t>
+  </si>
+  <si>
+    <t>International Schools Services</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b600fe584aea407ab7a32b1d27bcc64d-demand-generation-campaigns-strategist-international-schools-services-princeton</t>
+  </si>
+  <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Range Of Motion Project</t>
+  </si>
+  <si>
+    <t>Guatemala City, Guatemala Department, GT</t>
+  </si>
+  <si>
+    <t>USD 1250.00 - 1250.00/month</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb85ad3966114d6ba9db34b9b65e79d8-development-assistant-range-of-motion-project-guatemala-city</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT ASSISTANT/GRANT WRITER</t>
+  </si>
+  <si>
+    <t>Beautiful Day Granola</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Immigrants Or Refugees, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee561a3c225148fda51fe20eb74d00d4-development-assistantgrant-writer-beautiful-day-granola-providence</t>
+  </si>
+  <si>
+    <t>Development Officer, Major &amp; Institutional Giving</t>
+  </si>
+  <si>
+    <t>USD 95740.00 - 110408.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b642c8ffd674b5591d4f2bbe16b53d8-development-officer-major-institutional-giving-our-childrens-trust-eugene</t>
+  </si>
+  <si>
+    <t>Digital Fundraising Manager</t>
+  </si>
+  <si>
+    <t>Anera</t>
+  </si>
+  <si>
+    <t>USD 71313.00 - 76369.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b45cbe370c434e92a1b0f7af31ec9845-digital-fundraising-manager-anera-washington</t>
+  </si>
+  <si>
+    <t>Insight Meditation Community of Washington</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 95000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4ee400cf2bd4a1bac63c6ac774898c9-director-of-advancement-insight-meditation-community-of-washington-washington</t>
+  </si>
+  <si>
+    <t>Director of Community Engagement &amp; Development</t>
+  </si>
+  <si>
+    <t>Lydia Place A Nonprofit Corporation</t>
+  </si>
+  <si>
+    <t>Bellingham, Washington</t>
+  </si>
+  <si>
+    <t>USD 78357.00 - 94406.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c0a45770ee34c9b90cecd5516926cfc-director-of-community-engagement-development-lydia-place-a-nonprofit-corporation-bellingham</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Asian American Federation</t>
+  </si>
+  <si>
+    <t>USD 156000.00 - 176000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Civic Engagement, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4dcc502a0a8c477b860d8a4681a65b15-director-of-development-asian-american-federation-new-york</t>
+  </si>
+  <si>
+    <t>Neighborhood Music School</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8abcbfd9a9240fc8cb173cdb07a9740-director-of-development-neighborhood-music-school-new-haven</t>
+  </si>
+  <si>
+    <t>Director of Development Operations (Full Time, Remote)</t>
+  </si>
+  <si>
+    <t>Accelerate Change</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5370f61e832a4c10b1848e84e5117580-director-of-development-operations-full-time-remote-accelerate-change-boston</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>USD 126000.00 - 134000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Research Social Science, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2a46bcc40f5464c88a47b2c7cbc41d3-director-of-finance-asian-american-federation-new-york</t>
+  </si>
+  <si>
+    <t>Director of Major Gifts</t>
+  </si>
+  <si>
+    <t>The Phillips Collection</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21a671530ca848d887c3eaee2325c411-director-of-major-gifts-the-phillips-collection-washington</t>
+  </si>
+  <si>
+    <t>Director of Professional Development (Part-Time)</t>
+  </si>
+  <si>
+    <t>Editorial Freelancers Association</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a257a4c05e343e99f49bb745153fc5b-director-of-professional-development-part-time-editorial-freelancers-association-new-york</t>
+  </si>
+  <si>
+    <t>Director, Finance &amp; Accouting</t>
+  </si>
+  <si>
+    <t>AIDS SUPPORT GROUP OF CAPE COD INC</t>
+  </si>
+  <si>
+    <t>Provincetown, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a7f189c430c41f3af3926b7ff48640b-director-finance-accouting-aids-support-group-of-cape-cod-inc-provincetown</t>
+  </si>
+  <si>
+    <t>Director, Volunteer Programs and Fulfillment Centers</t>
+  </si>
+  <si>
+    <t>Metropolitan Council on Jewish Poverty</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/886c9b3e4d234df0842cae96fcc5d19c-director-volunteer-programs-and-fulfillment-centers-metropolitan-council-on-jewish-poverty-new-york</t>
+  </si>
+  <si>
+    <t>Emergency Services Manager</t>
+  </si>
+  <si>
+    <t>Rising Hope United Methodist Mission Church</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4a2d40d7fff4e5499e534a24bda2d64-emergency-services-manager-rising-hope-united-methodist-mission-church-alexandria</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>WAQRR - Washington Alliance for Quality Recovery Residences</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ac1f2ded9434b5b85f0dc78daf246b7-executive-director-waqrr-washington-alliance-for-quality-recovery-residences-mount-vernon</t>
+  </si>
+  <si>
+    <t>Faunalytics</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4eed178c727d4309951ad7e92f9eb111-executive-director-faunalytics-olympia</t>
+  </si>
+  <si>
+    <t>Own It: Building Black Wealth, Inc.</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/797435ff33f4452789601de5be57a786-executive-director-own-it-building-black-wealth-inc-madison</t>
+  </si>
+  <si>
+    <t>Executive Director of External Relations and Engagement (0457U), School of Social Welfare #88417</t>
+  </si>
+  <si>
+    <t>University of California, Berkeley</t>
+  </si>
+  <si>
+    <t>Berkeley, CA</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7b3c90dbf198406a9f843a24c3fca671-executive-director-of-external-relations-and-engagement-0457u-school-of-social-welfare-88417-university-of-california-berkeley-berkeley</t>
+  </si>
+  <si>
+    <t>Family Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>Youth Enrichment Services (YES)</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/49bdb990387d449a8197420177d42aec-family-engagement-coordinator-youth-enrichment-services-yes-boston</t>
+  </si>
+  <si>
+    <t>Fundraiser/Grant Writer</t>
+  </si>
+  <si>
+    <t>Vietnamese American Community Center of the East Bay</t>
+  </si>
+  <si>
+    <t>San Leandro, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/914474450af349f9b6712f8d43b21c9a-fundraisergrant-writer-vietnamese-american-community-center-of-the-east-bay-san-leandro</t>
+  </si>
+  <si>
+    <t>Government Contracts &amp; Proposal Supervisor</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae49ea5f913c456eb4a194688fa63a20-government-contracts-proposal-supervisor-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Grade 3-4 Learning Specialist (Leave Replacement)</t>
+  </si>
+  <si>
+    <t>The Allen-Stevenson School</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bd6d451ddd7450a8467a496a00c3d2a-grade-3-4-learning-specialist-leave-replacement-the-allen-stevenson-school-new-york</t>
+  </si>
+  <si>
+    <t>Grant Writer and Consultant - Independent Contractor</t>
+  </si>
+  <si>
+    <t>Prescott Circus Theatre</t>
+  </si>
+  <si>
+    <t>USD 600.00 - 850.00/week</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1a6460f9a034dfc9dd5aaaa386ac023-grant-writer-and-consultant-independent-contractor-prescott-circus-theatre-oakland</t>
+  </si>
+  <si>
+    <t>Grant Writing Consultant</t>
+  </si>
+  <si>
+    <t>Jewish Relief Agency (Philadelphia)</t>
+  </si>
+  <si>
+    <t>USD 3000.00/month</t>
+  </si>
+  <si>
+    <t>Poverty, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a66adbb82d6b4fac8a480b27cf872924-grant-writing-consultant-jewish-relief-agency-philadelphia-philadelphia</t>
+  </si>
+  <si>
+    <t>Group Teacher (Certified)</t>
+  </si>
+  <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/51a138112e2648e9942d3cc13583a2c6-group-teacher-certified-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>Group Teacher (Uncertified)</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f45efc04fb946c6a3b22a1d1d47cfb3-group-teacher-uncertified-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>Human Resources Director</t>
+  </si>
+  <si>
+    <t>Bradley Angle</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 112397.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6aa8d11d5a254a4bb2b29631b2e69b2a-human-resources-director-bradley-angle-portland</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/afed1cfcd3dc4659b8eba46e557a67aa-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Legal and Policy Associate</t>
+  </si>
+  <si>
+    <t>Center for Transnational Environmental Accountability</t>
+  </si>
+  <si>
+    <t>USD 47500.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/595c4e00fbd247148c210bb18c1d9da4-legal-and-policy-associate-center-for-transnational-environmental-accountability-washington</t>
+  </si>
+  <si>
+    <t>Media and Public Relations Manager</t>
+  </si>
+  <si>
+    <t>The Reporters Committee for Freedom of the Press</t>
+  </si>
+  <si>
+    <t>USD 73500.00 - 86800.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Media, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5ccde1708a4a4a1aba3ca3e82da4c75a-media-and-public-relations-manager-the-reporters-committee-for-freedom-of-the-press-washington</t>
+  </si>
+  <si>
+    <t>Museum Director</t>
+  </si>
+  <si>
+    <t>Idaho Military Museum</t>
+  </si>
+  <si>
+    <t>Boise, Idaho</t>
+  </si>
+  <si>
+    <t>USD 3500.00 - 7500.00/month</t>
+  </si>
+  <si>
+    <t>Education, Science Technology, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/752e954b4a4248ee9f5bfeca62619933-museum-director-idaho-military-museum-boise</t>
+  </si>
+  <si>
+    <t>NDRN Chief Operating Officer (COO)</t>
+  </si>
+  <si>
+    <t>National Disability Rights Network (NDRN)</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d20b9027d55d4b8ba65bffe06748367d-ndrn-chief-operating-officer-coo-national-disability-rights-network-ndrn-washington</t>
+  </si>
+  <si>
+    <t>Operations Administrator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/13ffaaaf5a6f410bb2e185c552d21f65-operations-administrator-youth-enrichment-services-yes-boston</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>The Record Co.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fdb1c0b797b8411788f893f43faf42a5-operations-manager-the-record-co-boston</t>
+  </si>
+  <si>
+    <t>Organizing Director</t>
+  </si>
+  <si>
+    <t>Center for Workers' Rights</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>Job Workplace, Legal Assistance, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a9f25e0fb3534ba183ee09b06889e71c-organizing-director-center-for-workers-rights-sacramento</t>
+  </si>
+  <si>
+    <t>Part Time Student Support Specialist (Evenings)</t>
+  </si>
+  <si>
+    <t>District 1199C Training &amp; Upgrading Fund</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fde8bedf69e04baab08b6da367db1789-part-time-student-support-specialist-evenings-district-1199c-training-upgrading-fund-philadelphia</t>
+  </si>
+  <si>
+    <t>People and Culture Manager</t>
+  </si>
+  <si>
+    <t>Meyer Memorial Trust</t>
+  </si>
+  <si>
+    <t>USD 103000.00 - 121000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11a2d060b8bb4709b325b43a11fa8157-people-and-culture-manager-meyer-memorial-trust-portland</t>
+  </si>
+  <si>
+    <t>Prestador/a de Servicios de Mantenimiento</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64e70cbd4362444b9812793f3fc42ad6-prestadora-de-servicios-de-mantenimiento-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Profesional para Trabajo Comunitario con Familias | Filial Mar del Plata</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e10cef6543c4c0f9f16450cac5f6dca-profesional-para-trabajo-comunitario-con-familias-filial-mar-del-plata-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Montgomery Coalition for Adult English Literacy</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 27000.00 - 32000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2c6ddb290a7a4cdf9bf29ef0f29daa83-program-assistant-montgomery-coalition-for-adult-english-literacy-rockville</t>
+  </si>
+  <si>
+    <t>Program Manager, Early Childhood</t>
+  </si>
+  <si>
+    <t>UnidosUS</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 82200.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43f620ad0c304961b887c28b3d84dd53-program-manager-early-childhood-unidosus-washington</t>
+  </si>
+  <si>
+    <t>Project Assistant</t>
+  </si>
+  <si>
+    <t>Council of Superior Court Clerks of Georgia</t>
+  </si>
+  <si>
+    <t>Remote (Georgia)</t>
+  </si>
+  <si>
+    <t>USD 43000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/35be541355944b34953b562a752d96c0-project-assistant-council-of-superior-court-clerks-of-georgia-atlanta</t>
+  </si>
+  <si>
+    <t>Project Manager of Real Estate Development</t>
+  </si>
+  <si>
+    <t>Allston Brighton Community Development Corporation</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5cf10707421049b9ad383b0b0530c8a5-project-manager-of-real-estate-development-allston-brighton-community-development-corporation-boston</t>
+  </si>
+  <si>
+    <t>Rachel’s Network President</t>
+  </si>
+  <si>
+    <t>Rachel's Network</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4382c05063b403ea14a9df82ca1402f-rachels-network-president-rachels-network-washington</t>
+  </si>
+  <si>
+    <t>Senior Director of Communications</t>
+  </si>
+  <si>
+    <t>American Business Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 185000.00 - 215000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b75bb7f48898455da786e0e808c9f208-senior-director-of-communications-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Senior Director of Policy and Government Affairs</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e308034712384ccdad2b284ec401df76-senior-director-of-policy-and-government-affairs-american-business-immigration-coalition-chicago</t>
+  </si>
+  <si>
+    <t>Senior Organizer</t>
+  </si>
+  <si>
+    <t>Popular Democracy</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/643f720933b44ceb8e5c0be96ddaaf13-senior-organizer-popular-democracy-brooklyn</t>
+  </si>
+  <si>
+    <t>Teaching Kitchen Program Manager</t>
+  </si>
+  <si>
+    <t>COMMUNITY SERVINGS INC</t>
+  </si>
+  <si>
+    <t>JAMAICA, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbbf66d2a6e74389821660bc3679f75d-teaching-kitchen-program-manager-community-servings-inc-jamaica</t>
+  </si>
+  <si>
+    <t>Temporary Volunteer Coordinator - Part-Time</t>
+  </si>
+  <si>
+    <t>Mansfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52e3883b9e154bb1b1da9d7e4ca5dfe0-temporary-volunteer-coordinator-part-time-community-servings-inc-mansfield</t>
+  </si>
+  <si>
+    <t>Vice President -- National Civic Art Society -- Classical Public Art and Architecture</t>
+  </si>
+  <si>
+    <t>National Civic Art Society</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84dd9309151a462cbfe5345ce5243555-vice-president-national-civic-art-society-classical-public-art-and-architecture-national-civic-art-society-washington</t>
+  </si>
+  <si>
+    <t>Vice President of Operations</t>
+  </si>
+  <si>
+    <t>Youth Eastside Services</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/01de1c3d8a3f49659e5f1ef07f3f959c-vice-president-of-operations-youth-eastside-services-bellevue</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1794,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1820,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2202,1018 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>98</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>103</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>133</v>
+      </c>
+      <c r="B27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" t="s">
+        <v>148</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>151</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>155</v>
+      </c>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" t="s">
+        <v>157</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E32" t="s">
+        <v>162</v>
+      </c>
+      <c r="F32" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" t="s">
+        <v>168</v>
+      </c>
+      <c r="F33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>171</v>
+      </c>
+      <c r="B34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" t="s">
+        <v>173</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B35" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>176</v>
+      </c>
+      <c r="F36" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>180</v>
+      </c>
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+      <c r="C37" t="s">
+        <v>182</v>
+      </c>
+      <c r="D37" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>186</v>
+      </c>
+      <c r="B38" t="s">
+        <v>187</v>
+      </c>
+      <c r="C38" t="s">
+        <v>188</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+      <c r="F38" t="s">
+        <v>190</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>192</v>
+      </c>
+      <c r="B39" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F39" t="s">
+        <v>157</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B40" t="s">
+        <v>196</v>
+      </c>
+      <c r="C40" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" t="s">
+        <v>197</v>
+      </c>
+      <c r="F40" t="s">
+        <v>198</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" t="s">
+        <v>182</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>114</v>
+      </c>
+      <c r="F41" t="s">
+        <v>184</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" t="s">
+        <v>204</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" t="s">
+        <v>206</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>208</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" t="s">
+        <v>209</v>
+      </c>
+      <c r="F43" t="s">
+        <v>210</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3260,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3295,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3334,1810 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" t="s">
+        <v>240</v>
+      </c>
+      <c r="E5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7" t="s">
+        <v>216</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E8" t="s">
+        <v>256</v>
+      </c>
+      <c r="F8" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" t="s">
+        <v>263</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F10" t="s">
+        <v>269</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C11" t="s">
+        <v>273</v>
+      </c>
+      <c r="D11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E11" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" t="s">
+        <v>216</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B12" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D12" t="s">
+        <v>240</v>
+      </c>
+      <c r="E12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" t="s">
+        <v>279</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C13" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" t="s">
+        <v>283</v>
+      </c>
+      <c r="F13" t="s">
+        <v>284</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B14" t="s">
+        <v>287</v>
+      </c>
+      <c r="C14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D14" t="s">
+        <v>222</v>
+      </c>
+      <c r="E14" t="s">
+        <v>289</v>
+      </c>
+      <c r="F14" t="s">
+        <v>290</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E15" t="s">
+        <v>294</v>
+      </c>
+      <c r="F15" t="s">
+        <v>295</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F16" t="s">
+        <v>302</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B17" t="s">
+        <v>305</v>
+      </c>
+      <c r="C17" t="s">
+        <v>306</v>
+      </c>
+      <c r="D17" t="s">
+        <v>222</v>
+      </c>
+      <c r="E17" t="s">
+        <v>307</v>
+      </c>
+      <c r="F17" t="s">
+        <v>308</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18" t="s">
+        <v>312</v>
+      </c>
+      <c r="D18" t="s">
+        <v>222</v>
+      </c>
+      <c r="E18" t="s">
+        <v>313</v>
+      </c>
+      <c r="F18" t="s">
+        <v>314</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B19" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" t="s">
+        <v>250</v>
+      </c>
+      <c r="D19" t="s">
+        <v>222</v>
+      </c>
+      <c r="E19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" t="s">
+        <v>318</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" t="s">
+        <v>322</v>
+      </c>
+      <c r="F20" t="s">
+        <v>323</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>325</v>
+      </c>
+      <c r="B21" t="s">
+        <v>326</v>
+      </c>
+      <c r="C21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" t="s">
+        <v>327</v>
+      </c>
+      <c r="F21" t="s">
+        <v>216</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>329</v>
+      </c>
+      <c r="B22" t="s">
+        <v>330</v>
+      </c>
+      <c r="C22" t="s">
+        <v>331</v>
+      </c>
+      <c r="D22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F22" t="s">
+        <v>332</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E23" t="s">
+        <v>216</v>
+      </c>
+      <c r="F23" t="s">
+        <v>216</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>338</v>
+      </c>
+      <c r="B24" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" t="s">
+        <v>340</v>
+      </c>
+      <c r="F24" t="s">
+        <v>290</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>342</v>
+      </c>
+      <c r="B25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" t="s">
+        <v>344</v>
+      </c>
+      <c r="D25" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" t="s">
+        <v>345</v>
+      </c>
+      <c r="F25" t="s">
+        <v>346</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" t="s">
+        <v>350</v>
+      </c>
+      <c r="D26" t="s">
+        <v>222</v>
+      </c>
+      <c r="E26" t="s">
+        <v>351</v>
+      </c>
+      <c r="F26" t="s">
+        <v>352</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>354</v>
+      </c>
+      <c r="B27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C27" t="s">
+        <v>250</v>
+      </c>
+      <c r="D27" t="s">
+        <v>222</v>
+      </c>
+      <c r="E27" t="s">
+        <v>355</v>
+      </c>
+      <c r="F27" t="s">
+        <v>284</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" t="s">
+        <v>250</v>
+      </c>
+      <c r="D28" t="s">
+        <v>222</v>
+      </c>
+      <c r="E28" t="s">
+        <v>359</v>
+      </c>
+      <c r="F28" t="s">
+        <v>360</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" t="s">
+        <v>362</v>
+      </c>
+      <c r="C29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" t="s">
+        <v>363</v>
+      </c>
+      <c r="E29" t="s">
+        <v>364</v>
+      </c>
+      <c r="F29" t="s">
+        <v>365</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" t="s">
+        <v>369</v>
+      </c>
+      <c r="D30" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" t="s">
+        <v>370</v>
+      </c>
+      <c r="F30" t="s">
+        <v>371</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B31" t="s">
+        <v>374</v>
+      </c>
+      <c r="C31" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" t="s">
+        <v>375</v>
+      </c>
+      <c r="F31" t="s">
+        <v>376</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>373</v>
+      </c>
+      <c r="B32" t="s">
+        <v>378</v>
+      </c>
+      <c r="C32" t="s">
+        <v>379</v>
+      </c>
+      <c r="D32" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" t="s">
+        <v>380</v>
+      </c>
+      <c r="F32" t="s">
+        <v>381</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>383</v>
+      </c>
+      <c r="B33" t="s">
+        <v>384</v>
+      </c>
+      <c r="C33" t="s">
+        <v>250</v>
+      </c>
+      <c r="D33" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" t="s">
+        <v>385</v>
+      </c>
+      <c r="F33" t="s">
+        <v>386</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>388</v>
+      </c>
+      <c r="B34" t="s">
+        <v>374</v>
+      </c>
+      <c r="C34" t="s">
+        <v>267</v>
+      </c>
+      <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>389</v>
+      </c>
+      <c r="F34" t="s">
+        <v>390</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" t="s">
+        <v>393</v>
+      </c>
+      <c r="C35" t="s">
+        <v>306</v>
+      </c>
+      <c r="D35" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" t="s">
+        <v>394</v>
+      </c>
+      <c r="F35" t="s">
+        <v>395</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>397</v>
+      </c>
+      <c r="B36" t="s">
+        <v>398</v>
+      </c>
+      <c r="C36" t="s">
+        <v>250</v>
+      </c>
+      <c r="D36" t="s">
+        <v>240</v>
+      </c>
+      <c r="E36" t="s">
+        <v>399</v>
+      </c>
+      <c r="F36" t="s">
+        <v>400</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>402</v>
+      </c>
+      <c r="B37" t="s">
+        <v>403</v>
+      </c>
+      <c r="C37" t="s">
+        <v>404</v>
+      </c>
+      <c r="D37" t="s">
+        <v>222</v>
+      </c>
+      <c r="E37" t="s">
+        <v>405</v>
+      </c>
+      <c r="F37" t="s">
+        <v>406</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>408</v>
+      </c>
+      <c r="B38" t="s">
+        <v>409</v>
+      </c>
+      <c r="C38" t="s">
+        <v>267</v>
+      </c>
+      <c r="D38" t="s">
+        <v>222</v>
+      </c>
+      <c r="E38" t="s">
+        <v>380</v>
+      </c>
+      <c r="F38" t="s">
+        <v>410</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>412</v>
+      </c>
+      <c r="B39" t="s">
+        <v>413</v>
+      </c>
+      <c r="C39" t="s">
+        <v>414</v>
+      </c>
+      <c r="D39" t="s">
+        <v>222</v>
+      </c>
+      <c r="E39" t="s">
+        <v>415</v>
+      </c>
+      <c r="F39" t="s">
+        <v>416</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>418</v>
+      </c>
+      <c r="B40" t="s">
+        <v>419</v>
+      </c>
+      <c r="C40" t="s">
+        <v>420</v>
+      </c>
+      <c r="D40" t="s">
+        <v>222</v>
+      </c>
+      <c r="E40" t="s">
+        <v>421</v>
+      </c>
+      <c r="F40" t="s">
+        <v>422</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>418</v>
+      </c>
+      <c r="B41" t="s">
+        <v>424</v>
+      </c>
+      <c r="C41" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" t="s">
+        <v>380</v>
+      </c>
+      <c r="F41" t="s">
+        <v>425</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>418</v>
+      </c>
+      <c r="B42" t="s">
+        <v>427</v>
+      </c>
+      <c r="C42" t="s">
+        <v>428</v>
+      </c>
+      <c r="D42" t="s">
+        <v>222</v>
+      </c>
+      <c r="E42" t="s">
+        <v>429</v>
+      </c>
+      <c r="F42" t="s">
+        <v>430</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>432</v>
+      </c>
+      <c r="B43" t="s">
+        <v>433</v>
+      </c>
+      <c r="C43" t="s">
+        <v>434</v>
+      </c>
+      <c r="D43" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" t="s">
+        <v>435</v>
+      </c>
+      <c r="F43" t="s">
+        <v>216</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>437</v>
+      </c>
+      <c r="B44" t="s">
+        <v>438</v>
+      </c>
+      <c r="C44" t="s">
+        <v>273</v>
+      </c>
+      <c r="D44" t="s">
+        <v>222</v>
+      </c>
+      <c r="E44" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s">
+        <v>439</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>441</v>
+      </c>
+      <c r="B45" t="s">
+        <v>442</v>
+      </c>
+      <c r="C45" t="s">
+        <v>443</v>
+      </c>
+      <c r="D45" t="s">
+        <v>222</v>
+      </c>
+      <c r="E45" t="s">
+        <v>444</v>
+      </c>
+      <c r="F45" t="s">
+        <v>323</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>446</v>
+      </c>
+      <c r="B46" t="s">
+        <v>447</v>
+      </c>
+      <c r="C46" t="s">
+        <v>267</v>
+      </c>
+      <c r="D46" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" t="s">
+        <v>448</v>
+      </c>
+      <c r="F46" t="s">
+        <v>449</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>451</v>
+      </c>
+      <c r="B47" t="s">
+        <v>452</v>
+      </c>
+      <c r="C47" t="s">
+        <v>267</v>
+      </c>
+      <c r="D47" t="s">
+        <v>363</v>
+      </c>
+      <c r="E47" t="s">
+        <v>453</v>
+      </c>
+      <c r="F47" t="s">
+        <v>290</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>455</v>
+      </c>
+      <c r="B48" t="s">
+        <v>456</v>
+      </c>
+      <c r="C48" t="s">
+        <v>234</v>
+      </c>
+      <c r="D48" t="s">
+        <v>300</v>
+      </c>
+      <c r="E48" t="s">
+        <v>457</v>
+      </c>
+      <c r="F48" t="s">
+        <v>458</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>460</v>
+      </c>
+      <c r="B49" t="s">
+        <v>461</v>
+      </c>
+      <c r="C49" t="s">
+        <v>250</v>
+      </c>
+      <c r="D49" t="s">
+        <v>300</v>
+      </c>
+      <c r="E49" t="s">
+        <v>462</v>
+      </c>
+      <c r="F49" t="s">
+        <v>463</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>465</v>
+      </c>
+      <c r="B50" t="s">
+        <v>466</v>
+      </c>
+      <c r="C50" t="s">
+        <v>267</v>
+      </c>
+      <c r="D50" t="s">
+        <v>222</v>
+      </c>
+      <c r="E50" t="s">
+        <v>467</v>
+      </c>
+      <c r="F50" t="s">
+        <v>237</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>469</v>
+      </c>
+      <c r="B51" t="s">
+        <v>466</v>
+      </c>
+      <c r="C51" t="s">
+        <v>267</v>
+      </c>
+      <c r="D51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" t="s">
+        <v>470</v>
+      </c>
+      <c r="F51" t="s">
+        <v>237</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>472</v>
+      </c>
+      <c r="B52" t="s">
+        <v>473</v>
+      </c>
+      <c r="C52" t="s">
+        <v>474</v>
+      </c>
+      <c r="D52" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" t="s">
+        <v>475</v>
+      </c>
+      <c r="F52" t="s">
+        <v>216</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>477</v>
+      </c>
+      <c r="B53" t="s">
+        <v>478</v>
+      </c>
+      <c r="C53" t="s">
+        <v>250</v>
+      </c>
+      <c r="D53" t="s">
+        <v>300</v>
+      </c>
+      <c r="E53" t="s">
+        <v>479</v>
+      </c>
+      <c r="F53" t="s">
+        <v>480</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>482</v>
+      </c>
+      <c r="B54" t="s">
+        <v>483</v>
+      </c>
+      <c r="C54" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" t="s">
+        <v>484</v>
+      </c>
+      <c r="F54" t="s">
+        <v>485</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>487</v>
+      </c>
+      <c r="B55" t="s">
+        <v>488</v>
+      </c>
+      <c r="C55" t="s">
+        <v>306</v>
+      </c>
+      <c r="D55" t="s">
+        <v>222</v>
+      </c>
+      <c r="E55" t="s">
+        <v>489</v>
+      </c>
+      <c r="F55" t="s">
+        <v>490</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>492</v>
+      </c>
+      <c r="B56" t="s">
+        <v>493</v>
+      </c>
+      <c r="C56" t="s">
+        <v>494</v>
+      </c>
+      <c r="D56" t="s">
+        <v>240</v>
+      </c>
+      <c r="E56" t="s">
+        <v>495</v>
+      </c>
+      <c r="F56" t="s">
+        <v>496</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>498</v>
+      </c>
+      <c r="B57" t="s">
+        <v>499</v>
+      </c>
+      <c r="C57" t="s">
+        <v>42</v>
+      </c>
+      <c r="D57" t="s">
+        <v>222</v>
+      </c>
+      <c r="E57" t="s">
+        <v>500</v>
+      </c>
+      <c r="F57" t="s">
+        <v>501</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>503</v>
+      </c>
+      <c r="B58" t="s">
+        <v>438</v>
+      </c>
+      <c r="C58" t="s">
+        <v>273</v>
+      </c>
+      <c r="D58" t="s">
+        <v>222</v>
+      </c>
+      <c r="E58" t="s">
+        <v>216</v>
+      </c>
+      <c r="F58" t="s">
+        <v>439</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>505</v>
+      </c>
+      <c r="B59" t="s">
+        <v>506</v>
+      </c>
+      <c r="C59" t="s">
+        <v>273</v>
+      </c>
+      <c r="D59" t="s">
+        <v>222</v>
+      </c>
+      <c r="E59" t="s">
+        <v>507</v>
+      </c>
+      <c r="F59" t="s">
+        <v>508</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>510</v>
+      </c>
+      <c r="B60" t="s">
+        <v>511</v>
+      </c>
+      <c r="C60" t="s">
+        <v>512</v>
+      </c>
+      <c r="D60" t="s">
+        <v>222</v>
+      </c>
+      <c r="E60" t="s">
+        <v>421</v>
+      </c>
+      <c r="F60" t="s">
+        <v>513</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>515</v>
+      </c>
+      <c r="B61" t="s">
+        <v>516</v>
+      </c>
+      <c r="C61" t="s">
+        <v>517</v>
+      </c>
+      <c r="D61" t="s">
+        <v>240</v>
+      </c>
+      <c r="E61" t="s">
+        <v>518</v>
+      </c>
+      <c r="F61" t="s">
+        <v>290</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>520</v>
+      </c>
+      <c r="B62" t="s">
+        <v>521</v>
+      </c>
+      <c r="C62" t="s">
+        <v>474</v>
+      </c>
+      <c r="D62" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" t="s">
+        <v>522</v>
+      </c>
+      <c r="F62" t="s">
+        <v>523</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>525</v>
+      </c>
+      <c r="B63" t="s">
+        <v>277</v>
+      </c>
+      <c r="C63" t="s">
+        <v>526</v>
+      </c>
+      <c r="D63" t="s">
+        <v>300</v>
+      </c>
+      <c r="E63" t="s">
+        <v>216</v>
+      </c>
+      <c r="F63" t="s">
+        <v>527</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>529</v>
+      </c>
+      <c r="B64" t="s">
+        <v>277</v>
+      </c>
+      <c r="C64" t="s">
+        <v>526</v>
+      </c>
+      <c r="D64" t="s">
+        <v>300</v>
+      </c>
+      <c r="E64" t="s">
+        <v>216</v>
+      </c>
+      <c r="F64" t="s">
+        <v>527</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>531</v>
+      </c>
+      <c r="B65" t="s">
+        <v>532</v>
+      </c>
+      <c r="C65" t="s">
+        <v>533</v>
+      </c>
+      <c r="D65" t="s">
+        <v>240</v>
+      </c>
+      <c r="E65" t="s">
+        <v>534</v>
+      </c>
+      <c r="F65" t="s">
+        <v>535</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>537</v>
+      </c>
+      <c r="B66" t="s">
+        <v>538</v>
+      </c>
+      <c r="C66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D66" t="s">
+        <v>222</v>
+      </c>
+      <c r="E66" t="s">
+        <v>539</v>
+      </c>
+      <c r="F66" t="s">
+        <v>540</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>542</v>
+      </c>
+      <c r="B67" t="s">
+        <v>543</v>
+      </c>
+      <c r="C67" t="s">
+        <v>544</v>
+      </c>
+      <c r="D67" t="s">
+        <v>300</v>
+      </c>
+      <c r="E67" t="s">
+        <v>545</v>
+      </c>
+      <c r="F67" t="s">
+        <v>546</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>548</v>
+      </c>
+      <c r="B68" t="s">
+        <v>549</v>
+      </c>
+      <c r="C68" t="s">
+        <v>273</v>
+      </c>
+      <c r="D68" t="s">
+        <v>222</v>
+      </c>
+      <c r="E68" t="s">
+        <v>550</v>
+      </c>
+      <c r="F68" t="s">
+        <v>535</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>552</v>
+      </c>
+      <c r="B69" t="s">
+        <v>553</v>
+      </c>
+      <c r="C69" t="s">
+        <v>306</v>
+      </c>
+      <c r="D69" t="s">
+        <v>222</v>
+      </c>
+      <c r="E69" t="s">
+        <v>554</v>
+      </c>
+      <c r="F69" t="s">
+        <v>555</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>557</v>
+      </c>
+      <c r="B70" t="s">
+        <v>558</v>
+      </c>
+      <c r="C70" t="s">
+        <v>250</v>
+      </c>
+      <c r="D70" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" t="s">
+        <v>559</v>
+      </c>
+      <c r="F70" t="s">
+        <v>323</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>561</v>
+      </c>
+      <c r="B71" t="s">
+        <v>558</v>
+      </c>
+      <c r="C71" t="s">
+        <v>562</v>
+      </c>
+      <c r="D71" t="s">
+        <v>222</v>
+      </c>
+      <c r="E71" t="s">
+        <v>559</v>
+      </c>
+      <c r="F71" t="s">
+        <v>323</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>564</v>
+      </c>
+      <c r="B72" t="s">
+        <v>565</v>
+      </c>
+      <c r="C72" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" t="s">
+        <v>448</v>
+      </c>
+      <c r="F72" t="s">
+        <v>566</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>568</v>
+      </c>
+      <c r="B73" t="s">
+        <v>569</v>
+      </c>
+      <c r="C73" t="s">
+        <v>570</v>
+      </c>
+      <c r="D73" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" t="s">
+        <v>571</v>
+      </c>
+      <c r="F73" t="s">
+        <v>572</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>574</v>
+      </c>
+      <c r="B74" t="s">
+        <v>569</v>
+      </c>
+      <c r="C74" t="s">
+        <v>575</v>
+      </c>
+      <c r="D74" t="s">
+        <v>235</v>
+      </c>
+      <c r="E74" t="s">
+        <v>576</v>
+      </c>
+      <c r="F74" t="s">
+        <v>572</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>578</v>
+      </c>
+      <c r="B75" t="s">
+        <v>579</v>
+      </c>
+      <c r="C75" t="s">
+        <v>250</v>
+      </c>
+      <c r="D75" t="s">
+        <v>222</v>
+      </c>
+      <c r="E75" t="s">
+        <v>580</v>
+      </c>
+      <c r="F75" t="s">
+        <v>581</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>583</v>
+      </c>
+      <c r="B76" t="s">
+        <v>584</v>
+      </c>
+      <c r="C76" t="s">
+        <v>585</v>
+      </c>
+      <c r="D76" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" t="s">
+        <v>289</v>
+      </c>
+      <c r="F76" t="s">
+        <v>586</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-15.xlsx
+++ b/docs/xlsx/jobs-2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1040">
   <si>
     <t>Title</t>
   </si>
@@ -673,6 +673,27 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/information-systems-technology-intern-3/</t>
   </si>
   <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Wild Virginia</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>40,000 - 60,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/operations-coordinator-6/</t>
+  </si>
+  <si>
     <t>Adult Protective Services Case Manager</t>
   </si>
   <si>
@@ -742,6 +763,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c660cad7b64b4b58acf44a3d8cff7ce6-after-school-program-assistant-oakland-kids-first-oakland</t>
   </si>
   <si>
+    <t>Analyst / Sr. Analyst (Spanish fluency required) - Remote, Part Time</t>
+  </si>
+  <si>
+    <t>Public Equity Group</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a39c951ef39c4f648a97fc9b3d6599df-analyst-sr-analyst-spanish-fluency-required-remote-part-time-public-equity-group-newburgh</t>
+  </si>
+  <si>
     <t>Assistant Educator [Federal Way]</t>
   </si>
   <si>
@@ -766,9 +802,6 @@
     <t>Partners In Health</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 70040.00 - 74160.00/year</t>
   </si>
   <si>
@@ -793,6 +826,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1dfd0bb5a74f4bd59c042850d43f8f6b-associate-director-for-individual-giving-development-american-library-association-chicago</t>
   </si>
   <si>
+    <t>Base Building Canvaser</t>
+  </si>
+  <si>
+    <t>VOCAL-KY</t>
+  </si>
+  <si>
+    <t>Louisville, Kentucky</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6dc038174499491ea06233b5b9fc93bf-base-building-canvaser-vocal-ky-louisville</t>
+  </si>
+  <si>
     <t>Business Analyst / Strategy &amp; Operations - Director's Associate - Chennai Residents Only</t>
   </si>
   <si>
@@ -859,6 +910,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/035edc34fc9c4c9e8b354f35a707c867-captadoresas-de-fondos-en-via-publica-para-caba-zona-oeste-aldeas-infantiles-sos-argentina-buenos-aires</t>
   </si>
   <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Hopelink</t>
+  </si>
+  <si>
+    <t>Redmond, Washington</t>
+  </si>
+  <si>
+    <t>USD 25.50 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Financial Literacy Personal Finance, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e01ddf5aec1f4868b77de7e41f29555b-case-manager-hopelink-redmond</t>
+  </si>
+  <si>
+    <t>CEO, Sixth &amp; I</t>
+  </si>
+  <si>
+    <t>Sixth &amp; I</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 230000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Religion Spirituality, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/565640bc7dcc4371843c0ab5dd1e25d9-ceo-sixth-i-sixth-i-washington</t>
+  </si>
+  <si>
     <t>Chief Advancement Officer</t>
   </si>
   <si>
@@ -892,6 +979,63 @@
     <t>https://www.idealist.org/en/nonprofit-job/3a1f16cee08e4b04bf2370a53ed37f4b-chief-financial-officer-la-promise-fund-los-angeles</t>
   </si>
   <si>
+    <t>Union Settlement Association</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 195000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a5e10c0a21ec4bf581f5ee429a541942-chief-financial-officer-union-settlement-association-new-york</t>
+  </si>
+  <si>
+    <t>Chief Officer of Marketing and Engagement</t>
+  </si>
+  <si>
+    <t>General Council Finance and Administration| The United Methodist Church</t>
+  </si>
+  <si>
+    <t>Nashville, Tennessee</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bb125b190397484686eafc5e659793e5-chief-officer-of-marketing-and-engagement-general-council-finance-and-administration-the-united-methodist-church-nashville</t>
+  </si>
+  <si>
+    <t>City-Wide Tenant Counselor</t>
+  </si>
+  <si>
+    <t>Housing Rights Committee of San Francisco</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 36.54 - 36.54/hour</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0768f9bbbca9439e8860bed5f4512e08-city-wide-tenant-counselor-housing-rights-committee-of-san-francisco-san-francisco</t>
+  </si>
+  <si>
+    <t>Client Relationship Manager</t>
+  </si>
+  <si>
+    <t>Life Managers &amp; Associates</t>
+  </si>
+  <si>
+    <t>Flourtown, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/8108c6c3ca7247c5b367ac512d0d48cb-client-relationship-manager-life-managers-associates-flourtown</t>
+  </si>
+  <si>
     <t>Client Services Case Manager</t>
   </si>
   <si>
@@ -907,6 +1051,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/b5ac982239f547e0b48af60ebc141b14-client-services-case-manager-medicare-rights-center-new-york</t>
   </si>
   <si>
+    <t>Clinical Coordinator, Adult Services</t>
+  </si>
+  <si>
+    <t>Our House NYC Grief Support Center</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b76ad04f654b40fa88337eb95af15b6b-clinical-coordinator-adult-services-our-house-nyc-grief-support-center-new-york</t>
+  </si>
+  <si>
+    <t>Communications and Partnership Manager</t>
+  </si>
+  <si>
+    <t>Farming Hope</t>
+  </si>
+  <si>
+    <t>USD 83500.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3722a05fafc14b9d8d8975487f0fe4e5-communications-and-partnership-manager-farming-hope-san-francisco</t>
+  </si>
+  <si>
     <t>Communications and Social Media Manager</t>
   </si>
   <si>
@@ -928,15 +1102,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/bee59221964f461b99c06cf859173ddd-communications-and-social-media-manager-massachusetts-chapter-of-the-american-academy-of-pediatrics-newton</t>
   </si>
   <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Jews for Racial &amp; Economic Justice</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b0c3fab413484c53ae949a53977051f7-communications-associate-jews-for-racial-economic-justice-new-york</t>
+  </si>
+  <si>
     <t>Communications Coordinator</t>
   </si>
   <si>
     <t>U.S. Grains &amp; BioProducts Council</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
     <t>USD 65000.00/year</t>
   </si>
   <si>
@@ -946,6 +1132,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/9e9c133a390d40f3b1f48020e4f7b23d-communications-coordinator-us-grains-bioproducts-council-washington</t>
   </si>
   <si>
+    <t>Communications Manager, Client Services</t>
+  </si>
+  <si>
+    <t>ReThink Media</t>
+  </si>
+  <si>
+    <t>USD 72500.00 - 90300.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Media, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/328070dbb5f749d49c21910bc378a0b1-communications-manager-client-services-rethink-media-washington</t>
+  </si>
+  <si>
+    <t>Communications Specialist / Senior Communications Specialist — U.S. &amp; Canada HDV and PV, plus Marine, Aviation, and Fuels</t>
+  </si>
+  <si>
+    <t>International Council on Clean Transportation</t>
+  </si>
+  <si>
+    <t>USD 114000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1c173dda9d749afa8a1e984ff03bec2-communications-specialist-senior-communications-specialist-us-canada-hdv-and-pv-plus-marine-aviation-and-fuels-international-council-on-clean-transportation-san-francisco</t>
+  </si>
+  <si>
+    <t>Community Health Research Associate</t>
+  </si>
+  <si>
+    <t>Institute for Community Health</t>
+  </si>
+  <si>
+    <t>Malden, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 64500.00 - 68500.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/950eb01e874744db85b1617a39cdb097-community-health-research-associate-institute-for-community-health-malden</t>
+  </si>
+  <si>
+    <t>Community Outreach Canvasser</t>
+  </si>
+  <si>
+    <t>Grassroots Voter Outreach</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ee89cfc64ad487bbd69892a2632defb-community-outreach-canvasser-grassroots-voter-outreach-denver</t>
+  </si>
+  <si>
     <t>Community Outreach Coordinator</t>
   </si>
   <si>
@@ -1030,6 +1282,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/ca9f595d36074f86b2dc3e90622f7e5b-coordinadora-de-operaciones-territoriales-norte-de-salta-asociacion-civil-pata-pila-tartagal</t>
   </si>
   <si>
+    <t>Data Center Fixed-Term Organizer</t>
+  </si>
+  <si>
+    <t>Stand (www.Stand.earth)</t>
+  </si>
+  <si>
+    <t>USD 27.64 - 40.87/hour</t>
+  </si>
+  <si>
+    <t>Environment, Environment, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44f7ea61fcf84708b1243c976c8e1ee0-data-center-fixed-term-organizer-stand-wwwstandearth-san-francisco</t>
+  </si>
+  <si>
+    <t>Data entry specialist</t>
+  </si>
+  <si>
+    <t>Positive Atmosphere Reaches Kids</t>
+  </si>
+  <si>
+    <t>Remote (Arkansas)</t>
+  </si>
+  <si>
+    <t>USD 27.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63e41f5b53464dbdae98a66fe0e0f05a-data-entry-specialist-positive-atmosphere-reaches-kids-little-rock</t>
+  </si>
+  <si>
     <t>Demand Generation Campaigns Strategist</t>
   </si>
   <si>
@@ -1042,6 +1327,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b600fe584aea407ab7a32b1d27bcc64d-demand-generation-campaigns-strategist-international-schools-services-princeton</t>
   </si>
   <si>
+    <t>Development and Operations Associate</t>
+  </si>
+  <si>
+    <t>Youth Advocacy Foundation</t>
+  </si>
+  <si>
+    <t>USD 59893.00 - 59893.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09dcff61138c4fa88ab0a6b143d0f3ea-development-and-operations-associate-youth-advocacy-foundation-boston</t>
+  </si>
+  <si>
     <t>Development Assistant</t>
   </si>
   <si>
@@ -1078,6 +1378,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/ee561a3c225148fda51fe20eb74d00d4-development-assistantgrant-writer-beautiful-day-granola-providence</t>
   </si>
   <si>
+    <t>Development Coordinator - WLADC</t>
+  </si>
+  <si>
+    <t>Ronald McDonald House Charities of Southern California</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Family, Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bfd04eec0d43425ea3e0bd4bd3695afb-development-coordinator-wladc-ronald-mcdonald-house-charities-of-southern-california-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>USD 83500.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c84f0c37c72459e8824e94a15027b91-development-manager-farming-hope-san-francisco</t>
+  </si>
+  <si>
+    <t>Turtle Island Restoration Network</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5db0e4e949ab4d75928b091ec36425b8-development-manager-turtle-island-restoration-network-olema</t>
+  </si>
+  <si>
     <t>Development Officer, Major &amp; Institutional Giving</t>
   </si>
   <si>
@@ -1102,6 +1441,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b45cbe370c434e92a1b0f7af31ec9845-digital-fundraising-manager-anera-washington</t>
   </si>
   <si>
+    <t>Digital Hub Project Manager (Independent Contractor Position)</t>
+  </si>
+  <si>
+    <t>Library Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Civic Engagement, Communications Access</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1b26a02bc38462197d14ec8bb4875a8-digital-hub-project-manager-independent-contractor-position-library-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Insight Meditation Community of Washington</t>
   </si>
   <si>
@@ -1192,6 +1546,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f2a46bcc40f5464c88a47b2c7cbc41d3-director-of-finance-asian-american-federation-new-york</t>
   </si>
   <si>
+    <t>Prevent Child Abuse - New Jersey</t>
+  </si>
+  <si>
+    <t>North Brunswick Township, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/116f48ffb43f47cb89331fe7150ebe08-director-of-finance-prevent-child-abuse-new-jersey-north-brunswick-township</t>
+  </si>
+  <si>
     <t>Director of Major Gifts</t>
   </si>
   <si>
@@ -1207,6 +1576,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/21a671530ca848d887c3eaee2325c411-director-of-major-gifts-the-phillips-collection-washington</t>
   </si>
   <si>
+    <t>Director of Organizing and Strategy, Downstate</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 98400.00 - 98400.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/143b41929fd6416697ff8c22dce9977d-director-of-organizing-and-strategy-downstate-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
     <t>Director of Professional Development (Part-Time)</t>
   </si>
   <si>
@@ -1222,6 +1606,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/8a257a4c05e343e99f49bb745153fc5b-director-of-professional-development-part-time-editorial-freelancers-association-new-york</t>
   </si>
   <si>
+    <t>Director, Corporate and Foundation Relations</t>
+  </si>
+  <si>
+    <t>Spoonfuls</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Hunger Food Security, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/903426d005ee47358cf4df2d5b35d9c8-director-corporate-and-foundation-relations-spoonfuls-newton</t>
+  </si>
+  <si>
     <t>Director, Finance &amp; Accouting</t>
   </si>
   <si>
@@ -1240,6 +1642,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/9a7f189c430c41f3af3926b7ff48640b-director-finance-accouting-aids-support-group-of-cape-cod-inc-provincetown</t>
   </si>
   <si>
+    <t>Director, Public Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>Southern California Grantmakers</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ab8ed6e6b82447f79b415f583eff2b0b-director-public-policy-advocacy-southern-california-grantmakers-los-angeles</t>
+  </si>
+  <si>
     <t>Director, Volunteer Programs and Fulfillment Centers</t>
   </si>
   <si>
@@ -1252,6 +1669,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/886c9b3e4d234df0842cae96fcc5d19c-director-volunteer-programs-and-fulfillment-centers-metropolitan-council-on-jewish-poverty-new-york</t>
   </si>
   <si>
+    <t>Dyslexia Barton Tutor</t>
+  </si>
+  <si>
+    <t>Uncommon Good</t>
+  </si>
+  <si>
+    <t>Pomona, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0861b94738ff4faea29368c037d1b73f-dyslexia-barton-tutor-uncommon-good-pomona</t>
+  </si>
+  <si>
     <t>Emergency Services Manager</t>
   </si>
   <si>
@@ -1270,6 +1705,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b4a2d40d7fff4e5499e534a24bda2d64-emergency-services-manager-rising-hope-united-methodist-mission-church-alexandria</t>
   </si>
   <si>
+    <t>Events and Community Outreach Manager</t>
+  </si>
+  <si>
+    <t>Brooklyn Conservatory of Music</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e8987aa8f8e846f5b98480b78ff74b85-events-and-community-outreach-manager-brooklyn-conservatory-of-music-kings-county</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1312,6 +1765,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/797435ff33f4452789601de5be57a786-executive-director-own-it-building-black-wealth-inc-madison</t>
   </si>
   <si>
+    <t>Avalonia Land Conservancy, Inc.</t>
+  </si>
+  <si>
+    <t>Ledyard, Connecticut</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c43e5cc41c034217ab46154635cdc8bc-executive-director-avalonia-land-conservancy-inc-ledyard</t>
+  </si>
+  <si>
     <t>Executive Director of External Relations and Engagement (0457U), School of Social Welfare #88417</t>
   </si>
   <si>
@@ -1354,6 +1816,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/914474450af349f9b6712f8d43b21c9a-fundraisergrant-writer-vietnamese-american-community-center-of-the-east-bay-san-leandro</t>
   </si>
   <si>
+    <t>GENERAL COUNSEL</t>
+  </si>
+  <si>
+    <t>Trust for Governors Island</t>
+  </si>
+  <si>
+    <t>USD 210000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Environment, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63a7daafcb6a444f9a304995fae0a85f-general-counsel-trust-for-governors-island-new-york</t>
+  </si>
+  <si>
     <t>Government Contracts &amp; Proposal Supervisor</t>
   </si>
   <si>
@@ -1414,9 +1891,6 @@
     <t>Group Teacher (Certified)</t>
   </si>
   <si>
-    <t>Union Settlement Association</t>
-  </si>
-  <si>
     <t>USD 56000.00 - 65000.00/year</t>
   </si>
   <si>
@@ -1432,6 +1906,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/8f45efc04fb946c6a3b22a1d1d47cfb3-group-teacher-uncertified-union-settlement-association-new-york</t>
   </si>
   <si>
+    <t>Housing and Resource Navigator</t>
+  </si>
+  <si>
+    <t>A Sense of Home</t>
+  </si>
+  <si>
+    <t>Hawthorne, California</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0117b19da41847a7b74be9f6142fbd46-housing-and-resource-navigator-a-sense-of-home-hawthorne</t>
+  </si>
+  <si>
+    <t>Human Resources &amp; Operations Director</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union (ACLU) of Arizona</t>
+  </si>
+  <si>
+    <t>Phoenix, Arizona</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96023a4d24ad4d069d9dbaef911f4365-human-resources-operations-director-american-civil-liberties-union-aclu-of-arizona-phoenix</t>
+  </si>
+  <si>
     <t>Human Resources Director</t>
   </si>
   <si>
@@ -1447,6 +1957,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/6aa8d11d5a254a4bb2b29631b2e69b2a-human-resources-director-bradley-angle-portland</t>
   </si>
   <si>
+    <t>Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>Cabrini Immigrant Services of NYC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e31fa77e8eb44a81a1716754ea34d6b1-immigration-staff-attorney-cabrini-immigrant-services-of-nyc-new-york</t>
+  </si>
+  <si>
     <t>International Director</t>
   </si>
   <si>
@@ -1462,6 +1981,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/afed1cfcd3dc4659b8eba46e557a67aa-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Remote (KR)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a6c5001c15e84127b37407b19d5790da-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Investment Associate</t>
+  </si>
+  <si>
+    <t>Partnership for New York City</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1bada68d0959472daa036d88472e663e-investment-associate-partnership-for-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>JOIN A PROGRESSIVE CAMPAIGN IN CALIFORNIA’S 48TH CONGRESSIONAL DISTRICT!</t>
+  </si>
+  <si>
+    <t>Worker Power</t>
+  </si>
+  <si>
+    <t>Moreno Valley, California</t>
+  </si>
+  <si>
+    <t>USD 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8aeecdeb363b4ab687ea04af6c221908-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-moreno-valley</t>
+  </si>
+  <si>
+    <t>Murrieta, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da97cd641c984031b09e991beeeb9178-join-a-progressive-campaign-in-californias-48th-congressional-district-worker-power-murrieta</t>
+  </si>
+  <si>
     <t>Legal and Policy Associate</t>
   </si>
   <si>
@@ -1477,6 +2038,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/595c4e00fbd247148c210bb18c1d9da4-legal-and-policy-associate-center-for-transnational-environmental-accountability-washington</t>
   </si>
   <si>
+    <t>Legal Support Analyst: Support Medicaid Fraud Investigations (6458)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>USD 69719.00 - 69719.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f88193d75a80459eb1e657ad649da14c-legal-support-analyst-support-medicaid-fraud-investigations-6458-new-york-state-office-of-the-attorney-general-new-york</t>
+  </si>
+  <si>
+    <t>Literacy Specialist- Awbury Campus</t>
+  </si>
+  <si>
+    <t>Wissahickon Charter School</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f119a094a40d4d3ba59dcaeb67c8f112-literacy-specialist-awbury-campus-wissahickon-charter-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Maintenance Engineer Eastern Region - Bend</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>Bend, Oregon</t>
+  </si>
+  <si>
+    <t>USD 32.69 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Media, Environment, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5de43bff776540208f929576d3b5a9f1-maintenance-engineer-eastern-region-bend-opb-bend</t>
+  </si>
+  <si>
+    <t>Manager of Employer Partnerships &amp; Career Placement</t>
+  </si>
+  <si>
+    <t>Trenton Area Soup Kitchen</t>
+  </si>
+  <si>
+    <t>Trenton, New Jersey</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34b495c3e2b3445f941302896ad5870f-manager-of-employer-partnerships-career-placement-trenton-area-soup-kitchen-trenton</t>
+  </si>
+  <si>
     <t>Media and Public Relations Manager</t>
   </si>
   <si>
@@ -1492,6 +2113,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/5ccde1708a4a4a1aba3ca3e82da4c75a-media-and-public-relations-manager-the-reporters-committee-for-freedom-of-the-press-washington</t>
   </si>
   <si>
+    <t>Medical Intake Manager</t>
+  </si>
+  <si>
+    <t>Make-A-Wish New Jersey</t>
+  </si>
+  <si>
+    <t>Monroe Township, NJ</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d80f045653b84aa3a79c23c7c3b8c60c-medical-intake-manager-make-a-wish-new-jersey-monroe-township</t>
+  </si>
+  <si>
     <t>Museum Director</t>
   </si>
   <si>
@@ -1531,6 +2167,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/13ffaaaf5a6f410bb2e185c552d21f65-operations-administrator-youth-enrichment-services-yes-boston</t>
   </si>
   <si>
+    <t>USD 31.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59fc6790677d41ddb0a955ee6a81a82c-operations-coordinator-jews-for-racial-economic-justice-new-york</t>
+  </si>
+  <si>
     <t>Operations Manager</t>
   </si>
   <si>
@@ -1567,15 +2212,27 @@
     <t>District 1199C Training &amp; Upgrading Fund</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 35.00 - 35.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/fde8bedf69e04baab08b6da367db1789-part-time-student-support-specialist-evenings-district-1199c-training-upgrading-fund-philadelphia</t>
   </si>
   <si>
+    <t>Partnerships, Resource Development &amp; Sustainability Consultant</t>
+  </si>
+  <si>
+    <t>An Emerging Culinary, Culture &amp; Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 5000.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a971e761e49644c8b2d9c5e80c4de2bc-partnerships-resource-development-sustainability-consultant-an-emerging-culinary-culture-community-foundation-new-york</t>
+  </si>
+  <si>
     <t>People and Culture Manager</t>
   </si>
   <si>
@@ -1585,12 +2242,45 @@
     <t>USD 103000.00 - 121000.00/year</t>
   </si>
   <si>
-    <t>Philanthropy</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/11a2d060b8bb4709b325b43a11fa8157-people-and-culture-manager-meyer-memorial-trust-portland</t>
   </si>
   <si>
+    <t>PHILANTHROPY FELLOW, CIVIL SOCIETY AND LEADERSHIP</t>
+  </si>
+  <si>
+    <t>UC Berkeley Haas Center for Social Sector Leadership</t>
+  </si>
+  <si>
+    <t>Los Altos, California</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d8f96fb72554c46ad1644f92437eacc-philanthropy-fellow-civil-society-and-leadership-uc-berkeley-haas-center-for-social-sector-leadership-los-altos</t>
+  </si>
+  <si>
+    <t>Philanthropy Operations Manager</t>
+  </si>
+  <si>
+    <t>Covenant House Michigan</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c9e383ef9c034bb98300e286aafdb7c0-philanthropy-operations-manager-covenant-house-michigan-detroit</t>
+  </si>
+  <si>
     <t>Prestador/a de Servicios de Mantenimiento</t>
   </si>
   <si>
@@ -1603,6 +2293,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/64e70cbd4362444b9812793f3fc42ad6-prestadora-de-servicios-de-mantenimiento-aldeas-infantiles-sos-argentina-mar-del-plata</t>
   </si>
   <si>
+    <t>Pro Bono Director</t>
+  </si>
+  <si>
+    <t>Inland Counties Legal Services, Inc.</t>
+  </si>
+  <si>
+    <t>Riverside, California</t>
+  </si>
+  <si>
+    <t>USD 127920.00 - 150800.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f9805ef10ed4015a91dee0c70ee00c2-pro-bono-director-inland-counties-legal-services-inc-riverside</t>
+  </si>
+  <si>
     <t>Profesional para Trabajo Comunitario con Familias | Filial Mar del Plata</t>
   </si>
   <si>
@@ -1621,9 +2329,6 @@
     <t>USD 27000.00 - 32000.00/year</t>
   </si>
   <si>
-    <t>Civic Engagement, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/2c6ddb290a7a4cdf9bf29ef0f29daa83-program-assistant-montgomery-coalition-for-adult-english-literacy-rockville</t>
   </si>
   <si>
@@ -1666,12 +2371,24 @@
     <t>Allston Brighton Community Development Corporation</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5cf10707421049b9ad383b0b0530c8a5-project-manager-of-real-estate-development-allston-brighton-community-development-corporation-boston</t>
   </si>
   <si>
+    <t>Quality Improvement Specialist | Mid-Hudson</t>
+  </si>
+  <si>
+    <t>NY Early Childhood Professional Development Institute</t>
+  </si>
+  <si>
+    <t>Poughkeepsie, New York</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa3dfe0c90744f3dad3d39a243ec4810-quality-improvement-specialist-mid-hudson-ny-early-childhood-professional-development-institute-poughkeepsie</t>
+  </si>
+  <si>
     <t>Rachel’s Network President</t>
   </si>
   <si>
@@ -1687,6 +2404,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b4382c05063b403ea14a9df82ca1402f-rachels-network-president-rachels-network-washington</t>
   </si>
   <si>
+    <t>Research Operations Coordinator</t>
+  </si>
+  <si>
+    <t>National Down Syndrome Society</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ddfd73f695114240b0339ae0a02781ed-research-operations-coordinator-national-down-syndrome-society-washington</t>
+  </si>
+  <si>
     <t>Senior Director of Communications</t>
   </si>
   <si>
@@ -1708,18 +2440,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/e308034712384ccdad2b284ec401df76-senior-director-of-policy-and-government-affairs-american-business-immigration-coalition-chicago</t>
   </si>
   <si>
+    <t>Senior Manager, Financial Planning &amp; Analysis (FP&amp;A)</t>
+  </si>
+  <si>
+    <t>Spark MicroGrants</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bbc26f4419604d6d934335fc304f521e-senior-manager-financial-planning-analysis-fpa-spark-microgrants-new-york</t>
+  </si>
+  <si>
     <t>Senior Organizer</t>
   </si>
   <si>
     <t>Popular Democracy</t>
   </si>
   <si>
-    <t>Community Development, Economic Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/643f720933b44ceb8e5c0be96ddaaf13-senior-organizer-popular-democracy-brooklyn</t>
   </si>
   <si>
+    <t>Sponsorship Director for Charity Bike Ride</t>
+  </si>
+  <si>
+    <t>LIVE THE BAY</t>
+  </si>
+  <si>
+    <t>ALAMEDA, California</t>
+  </si>
+  <si>
+    <t>Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c4e3472f37584451a74f5f7feae7bf9f-sponsorship-director-for-charity-bike-ride-live-the-bay-alameda</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>USD 88900.00 - 91500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efbb3068749f459cb471c8c278b82492-staff-attorney-american-civil-liberties-union-aclu-of-arizona-phoenix</t>
+  </si>
+  <si>
+    <t>Strategy, Programs &amp; Organizational Development Consultant</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/218250d915f24cf9b9fd240fb3f140ee-strategy-programs-organizational-development-consultant-an-emerging-culinary-culture-community-foundation-new-york</t>
+  </si>
+  <si>
     <t>Teaching Kitchen Program Manager</t>
   </si>
   <si>
@@ -1750,6 +2521,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/52e3883b9e154bb1b1da9d7e4ca5dfe0-temporary-volunteer-coordinator-part-time-community-servings-inc-mansfield</t>
   </si>
   <si>
+    <t>Transportation Research Analyst</t>
+  </si>
+  <si>
+    <t>American Council for an Energy-Efficient Economy</t>
+  </si>
+  <si>
+    <t>USD 57378.00 - 71722.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/38d5616377c64df0b3d822ced3723064-transportation-research-analyst-american-council-for-an-energy-efficient-economy-washington</t>
+  </si>
+  <si>
+    <t>Tutor</t>
+  </si>
+  <si>
+    <t>Southeast Community Foundation</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2886cfcc3b864bc7954958b65f91229d-tutor-southeast-community-foundation-los-angeles</t>
+  </si>
+  <si>
+    <t>Vegetable Field &amp; Crew Lead Position at Three Springs Community Farm</t>
+  </si>
+  <si>
+    <t>Three Springs Community Farm Foundation</t>
+  </si>
+  <si>
+    <t>Freestone, CA</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 31.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/293adfc72d75413cb70e3a7259c7c7fc-vegetable-field-crew-lead-position-at-three-springs-community-farm-three-springs-community-farm-foundation-freestone</t>
+  </si>
+  <si>
     <t>Vice President -- National Civic Art Society -- Classical Public Art and Architecture</t>
   </si>
   <si>
@@ -1778,6 +2597,543 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/01de1c3d8a3f49659e5f1ef07f3f959c-vice-president-of-operations-youth-eastside-services-bellevue</t>
+  </si>
+  <si>
+    <t>Volunteer Recruiter for 2027 Bay Ride</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a674d47b8ba34ca4b2068427f70095f9-volunteer-recruiter-for-2027-bay-ride-live-the-bay-alameda</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Advocate - Urban Wildlands</t>
+  </si>
+  <si>
+    <t>Center for Biological Diversity</t>
+  </si>
+  <si>
+    <t>USD 63600.00 - 91000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/461df7eb0abc459bb0120ad3b3935ff8-wildlife-conservation-advocate-urban-wildlands-center-for-biological-diversity-oakland</t>
+  </si>
+  <si>
+    <t>Workforce Readiness Specialist</t>
+  </si>
+  <si>
+    <t>USD 48500.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a81e0cd03e14283b4e0e69def1eb0f0-workforce-readiness-specialist-trenton-area-soup-kitchen-trenton</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE ASSOCIATE</t>
+  </si>
+  <si>
+    <t>Vermont Foodbank</t>
+  </si>
+  <si>
+    <t>Barre, Vermont</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73182815</t>
+  </si>
+  <si>
+    <t>ADVOCATE</t>
+  </si>
+  <si>
+    <t>Natural Resources Defense Council</t>
+  </si>
+  <si>
+    <t>Policy &amp; Advocacy</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73208477</t>
+  </si>
+  <si>
+    <t>APPRENTICE GROWER</t>
+  </si>
+  <si>
+    <t>Bright Farms</t>
+  </si>
+  <si>
+    <t>Yorkville, Illinois</t>
+  </si>
+  <si>
+    <t>Program Operations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73193813</t>
+  </si>
+  <si>
+    <t>ASSOCIATE DEAN OF OPERATIONS AND EXTERNAL RELATIONS</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73171817</t>
+  </si>
+  <si>
+    <t>CERTIFICATION DIRECTOR</t>
+  </si>
+  <si>
+    <t>MOSA Certified Organic</t>
+  </si>
+  <si>
+    <t>Viroqua, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73220697</t>
+  </si>
+  <si>
+    <t>CHIEF INFORMATION SECURITY OFFICER</t>
+  </si>
+  <si>
+    <t>University of California Agriculture and Natural Resources</t>
+  </si>
+  <si>
+    <t>Davis, California</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73181593</t>
+  </si>
+  <si>
+    <t>CLIMATE AND OCEANS CAMPAIGNER</t>
+  </si>
+  <si>
+    <t>Friends of the Earth</t>
+  </si>
+  <si>
+    <t>Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73210921</t>
+  </si>
+  <si>
+    <t>CLIMATE SMART MARKETS PROGRAM AND GRANT SPECIALIST</t>
+  </si>
+  <si>
+    <t>GRANT SPECIALIST IV - Colorado Department of Agriculture</t>
+  </si>
+  <si>
+    <t>Broomfield County, Colorado</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73176705</t>
+  </si>
+  <si>
+    <t>COALITION SECRETARIAT AND ENGAGEMENT ASSOCIATE</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73179149</t>
+  </si>
+  <si>
+    <t>COMMUNITY NUTRITION MANAGER</t>
+  </si>
+  <si>
+    <t>Food Bank of Central and Eastern North Carolina</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73197479</t>
+  </si>
+  <si>
+    <t>DATA ANALYST â€“ FARMER CONTRACTING AND REPORTING</t>
+  </si>
+  <si>
+    <t>AgOutcomes</t>
+  </si>
+  <si>
+    <t>Ankeny, Iowa</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73201145</t>
+  </si>
+  <si>
+    <t>DEPUTY DIRECTOR OF FOOD POLICY</t>
+  </si>
+  <si>
+    <t>CITY PLANNER SUPERVISOR - DEPARTMENT OF PLANNING - City of Baltimore</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73180371</t>
+  </si>
+  <si>
+    <t>DIRECTOR</t>
+  </si>
+  <si>
+    <t>COMMUNITY ENGAGEMENT - NATIVE-TRIBAL COMMUNITIES - Feeding American</t>
+  </si>
+  <si>
+    <t>Hybrid in Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73169373</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF ADVOCACY</t>
+  </si>
+  <si>
+    <t>St Louis Area Food Bank</t>
+  </si>
+  <si>
+    <t>St. Louis, Missouri</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73212143</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF ENGAGEMENT AND STATE RELATIONS</t>
+  </si>
+  <si>
+    <t>School Nutrition Association</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73168151</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF PROGRAMS</t>
+  </si>
+  <si>
+    <t>Wasatch Community Gardens</t>
+  </si>
+  <si>
+    <t>Salt Lake City, Utah</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73202367</t>
+  </si>
+  <si>
+    <t>END FOOD WASTE CAMPAIGN ASSOCIATE</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73214587</t>
+  </si>
+  <si>
+    <t>EXECUTIVE DIRECTOR</t>
+  </si>
+  <si>
+    <t>Just Roots</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73185259</t>
+  </si>
+  <si>
+    <t>FIELD OPERATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73199923</t>
+  </si>
+  <si>
+    <t>FIELD PROGRAM LEAD</t>
+  </si>
+  <si>
+    <t>BIOFUELS - AgOutcomes</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73198701</t>
+  </si>
+  <si>
+    <t>FOOD SECURITY AND BASIC NEEDS PROGRAM COORDINATOR</t>
+  </si>
+  <si>
+    <t>Montgomery College</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73215809</t>
+  </si>
+  <si>
+    <t>FOOD SYSTEMS AND NUTRITION COORDINATOR</t>
+  </si>
+  <si>
+    <t>University of Missouri</t>
+  </si>
+  <si>
+    <t>Columbia, Missouri</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73217031</t>
+  </si>
+  <si>
+    <t>FOOD SYSTEMS DIRECTOR</t>
+  </si>
+  <si>
+    <t>Open Cupboard</t>
+  </si>
+  <si>
+    <t>Maplewood, Minnesota</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73196257</t>
+  </si>
+  <si>
+    <t>GARDEN AND CULINARY PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>Blue Watermelon Project</t>
+  </si>
+  <si>
+    <t>Scottsdale, Arizona</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73192591</t>
+  </si>
+  <si>
+    <t>GLOBAL INITIATIVES DIRECTOR</t>
+  </si>
+  <si>
+    <t>GLOBAL FOOD INSTITUTE - George Washington University</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73186481</t>
+  </si>
+  <si>
+    <t>LIVESTOCK CERTIFICATION SPECIALIST</t>
+  </si>
+  <si>
+    <t>NOFA NY</t>
+  </si>
+  <si>
+    <t>Not Stated, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73170595</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>FOOD SYSTEMS AND NUTRITION - Cook County Health and Hospitals Systems</t>
+  </si>
+  <si>
+    <t>Forest Park, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73184037</t>
+  </si>
+  <si>
+    <t>FOOD WASTE WARRIOR PROGRAM - World Wildlife Fund</t>
+  </si>
+  <si>
+    <t>Hybrid in Washington DC, Washington DC</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73207255</t>
+  </si>
+  <si>
+    <t>MARKET EXPANSION PROGRAM MANAGER</t>
+  </si>
+  <si>
+    <t>GRANT SPECIALIST V - Colorado Department of Agriculture</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73175483</t>
+  </si>
+  <si>
+    <t>MARKETING COORDINATOR</t>
+  </si>
+  <si>
+    <t>Retaaza</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73166929</t>
+  </si>
+  <si>
+    <t>MOBILE MARKET OPERATOR</t>
+  </si>
+  <si>
+    <t>PART TIME - The Peoples Market</t>
+  </si>
+  <si>
+    <t>Hyattsville, Maryland</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73188925</t>
+  </si>
+  <si>
+    <t>NEW YORK PROGRAM ASSOCIATE</t>
+  </si>
+  <si>
+    <t>American Farmland Trust</t>
+  </si>
+  <si>
+    <t>Remote within 2 hours of Saratoga Springs, New Yor</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73190147</t>
+  </si>
+  <si>
+    <t>PROCUREMENT COORDINATOR</t>
+  </si>
+  <si>
+    <t>FOOD PROGRAMS - MET Council</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73218253</t>
+  </si>
+  <si>
+    <t>PROGRAM ASSOCIATE â€“ US PROGRAMS</t>
+  </si>
+  <si>
+    <t>Waverley Street Foundation</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73219475</t>
+  </si>
+  <si>
+    <t>PROGRAM OPERATIONS SPECIALIST</t>
+  </si>
+  <si>
+    <t>Non GMO Project</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73177927</t>
+  </si>
+  <si>
+    <t>RECEIVING COORDINATOR</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73213365</t>
+  </si>
+  <si>
+    <t>RESEARCH AND POLICY MANAGER</t>
+  </si>
+  <si>
+    <t>AGRICULTURE - University of Chicago</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73221919</t>
+  </si>
+  <si>
+    <t>SENIOR ASSOCIATE</t>
+  </si>
+  <si>
+    <t>CORPORATE PARTNERSHIPS - World Food Program USA</t>
+  </si>
+  <si>
+    <t>Fund Development</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73165707</t>
+  </si>
+  <si>
+    <t>SENIOR POLICY ADVOCATE GLOBAL FINANCE AND FOOD SYSTEMS</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73209699</t>
+  </si>
+  <si>
+    <t>SENIOR PROGRAM OFFICER</t>
+  </si>
+  <si>
+    <t>FOOD NUTRITION AND AGRICULTURE PROGRAM - Center for Health and People and Places</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73174261</t>
+  </si>
+  <si>
+    <t>SOUS CHEF</t>
+  </si>
+  <si>
+    <t>Round the Bend Farm</t>
+  </si>
+  <si>
+    <t>South Dartmouth, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73191369</t>
+  </si>
+  <si>
+    <t>STAFF ATTORNEY</t>
+  </si>
+  <si>
+    <t>FarmSTAND</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73195035</t>
+  </si>
+  <si>
+    <t>SUSTAINABLE RANCHING INITIATIVE SPECIALIST</t>
+  </si>
+  <si>
+    <t>World Wildlife Fund</t>
+  </si>
+  <si>
+    <t>Bozeman, Montana</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73204811</t>
+  </si>
+  <si>
+    <t>TEXAS MANAGER OF PROGRAM IMPACT</t>
+  </si>
+  <si>
+    <t>FoodCorps</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73206033</t>
+  </si>
+  <si>
+    <t>VICE PRESIDENT</t>
+  </si>
+  <si>
+    <t>CATALYTIC CAPITAL - Food System Innovations</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73203589</t>
+  </si>
+  <si>
+    <t>VISITING EXTENSION OUTREACH ASSISTANT</t>
+  </si>
+  <si>
+    <t>HEALTH AND COMMUNITY WELLNESS - University of Illinois Extension</t>
+  </si>
+  <si>
+    <t>Urbana, Illinois</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73173039</t>
+  </si>
+  <si>
+    <t>YOUTH FARMER SPECIALIST</t>
+  </si>
+  <si>
+    <t>The Opportunity Hub</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=73187703</t>
   </si>
 </sst>
 </file>
@@ -3221,7 +4577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3283,10 +4639,34 @@
         <v>218</v>
       </c>
     </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3295,7 +4675,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3336,1727 +4716,3084 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F2" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D6" t="s">
         <v>242</v>
       </c>
-      <c r="B6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" t="s">
-        <v>240</v>
-      </c>
       <c r="E6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F6" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D7" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E7" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C8" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="F8" t="s">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D9" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C11" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B12" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C12" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E12" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="D13" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F13" t="s">
-        <v>284</v>
+        <v>216</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C14" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>289</v>
+        <v>216</v>
       </c>
       <c r="F14" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="F15" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B16" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C16" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E16" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B17" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C17" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="D17" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F17" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C18" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D18" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E18" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F18" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B19" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C19" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D19" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E19" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="F19" t="s">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B20" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C20" t="s">
-        <v>267</v>
+        <v>326</v>
       </c>
       <c r="D20" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E20" t="s">
-        <v>322</v>
+        <v>216</v>
       </c>
       <c r="F20" t="s">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B21" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C21" t="s">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="D21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E21" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F21" t="s">
-        <v>216</v>
+        <v>332</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="D22" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s">
-        <v>216</v>
+        <v>337</v>
       </c>
       <c r="F22" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B23" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C23" t="s">
-        <v>336</v>
+        <v>284</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s">
-        <v>216</v>
+        <v>342</v>
       </c>
       <c r="F23" t="s">
-        <v>216</v>
+        <v>343</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B24" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C24" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D24" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E24" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F24" t="s">
-        <v>290</v>
+        <v>348</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B25" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C25" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="F25" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B26" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="C26" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D26" t="s">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="E26" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F26" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B27" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
       <c r="C27" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D27" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E27" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F27" t="s">
-        <v>284</v>
+        <v>365</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B28" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C28" t="s">
-        <v>250</v>
+        <v>306</v>
       </c>
       <c r="D28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E28" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>372</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C29" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
-        <v>363</v>
+        <v>229</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F29" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C30" t="s">
-        <v>369</v>
+        <v>330</v>
       </c>
       <c r="D30" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E30" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="F30" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B31" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C31" t="s">
-        <v>267</v>
+        <v>384</v>
       </c>
       <c r="D31" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E31" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F31" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B32" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="C32" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="D32" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E32" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F32" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B33" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C33" t="s">
-        <v>250</v>
+        <v>396</v>
       </c>
       <c r="D33" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E33" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="F33" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B34" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="C34" t="s">
-        <v>267</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E34" t="s">
-        <v>389</v>
+        <v>216</v>
       </c>
       <c r="F34" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B35" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C35" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D35" t="s">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="E35" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F35" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B36" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C36" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D36" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E36" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F36" t="s">
-        <v>400</v>
+        <v>216</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B37" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="C37" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="D37" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E37" t="s">
-        <v>405</v>
+        <v>216</v>
       </c>
       <c r="F37" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B38" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="C38" t="s">
-        <v>267</v>
+        <v>420</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E38" t="s">
-        <v>380</v>
+        <v>216</v>
       </c>
       <c r="F38" t="s">
-        <v>410</v>
+        <v>216</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B39" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="C39" t="s">
-        <v>414</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="E39" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F39" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B40" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C40" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="D40" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E40" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="F40" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>418</v>
+        <v>433</v>
       </c>
       <c r="B41" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="C41" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D41" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E41" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="F41" t="s">
-        <v>425</v>
+        <v>319</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="B42" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C42" t="s">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="D42" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E42" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="F42" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="B43" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="C43" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D43" t="s">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="E43" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F43" t="s">
-        <v>216</v>
+        <v>446</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="B44" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C44" t="s">
-        <v>273</v>
+        <v>450</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E44" t="s">
-        <v>216</v>
+        <v>451</v>
       </c>
       <c r="F44" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="B45" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="C45" t="s">
-        <v>443</v>
+        <v>317</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E45" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F45" t="s">
-        <v>323</v>
+        <v>457</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="B46" t="s">
-        <v>447</v>
+        <v>351</v>
       </c>
       <c r="C46" t="s">
-        <v>267</v>
+        <v>330</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="F46" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B47" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C47" t="s">
-        <v>267</v>
+        <v>464</v>
       </c>
       <c r="D47" t="s">
-        <v>363</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
-        <v>453</v>
+        <v>342</v>
       </c>
       <c r="F47" t="s">
-        <v>290</v>
+        <v>465</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B48" t="s">
-        <v>456</v>
+        <v>311</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="D48" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E48" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F48" t="s">
-        <v>458</v>
+        <v>313</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="B49" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="C49" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E49" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="F49" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="B50" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="C50" t="s">
-        <v>267</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>358</v>
       </c>
       <c r="E50" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="F50" t="s">
-        <v>237</v>
+        <v>478</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>469</v>
+        <v>62</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="C51" t="s">
-        <v>267</v>
+        <v>306</v>
       </c>
       <c r="D51" t="s">
-        <v>222</v>
+        <v>481</v>
       </c>
       <c r="E51" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="F51" t="s">
-        <v>237</v>
+        <v>483</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="B52" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="C52" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="D52" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E52" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="F52" t="s">
-        <v>216</v>
+        <v>489</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E53" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F53" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>497</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E54" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="F54" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C55" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="F55" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>506</v>
+      </c>
+      <c r="B56" t="s">
         <v>492</v>
       </c>
-      <c r="B56" t="s">
-        <v>493</v>
-      </c>
       <c r="C56" t="s">
-        <v>494</v>
+        <v>284</v>
       </c>
       <c r="D56" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E56" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="F56" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B57" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="C57" t="s">
-        <v>42</v>
+        <v>511</v>
       </c>
       <c r="D57" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E57" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="F57" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="B58" t="s">
-        <v>438</v>
+        <v>516</v>
       </c>
       <c r="C58" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="D58" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E58" t="s">
-        <v>216</v>
+        <v>517</v>
       </c>
       <c r="F58" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>504</v>
+        <v>519</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s">
-        <v>506</v>
+        <v>521</v>
       </c>
       <c r="C59" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D59" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E59" t="s">
-        <v>507</v>
+        <v>522</v>
       </c>
       <c r="F59" t="s">
-        <v>508</v>
+        <v>523</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="B60" t="s">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c r="C60" t="s">
-        <v>512</v>
+        <v>221</v>
       </c>
       <c r="D60" t="s">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="E60" t="s">
-        <v>421</v>
+        <v>527</v>
       </c>
       <c r="F60" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="C61" t="s">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="D61" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E61" t="s">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="F61" t="s">
-        <v>290</v>
+        <v>534</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B62" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="C62" t="s">
-        <v>474</v>
+        <v>538</v>
       </c>
       <c r="D62" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E62" t="s">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="F62" t="s">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="B63" t="s">
-        <v>277</v>
+        <v>543</v>
       </c>
       <c r="C63" t="s">
-        <v>526</v>
+        <v>317</v>
       </c>
       <c r="D63" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E63" t="s">
-        <v>216</v>
+        <v>544</v>
       </c>
       <c r="F63" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="B64" t="s">
-        <v>277</v>
+        <v>548</v>
       </c>
       <c r="C64" t="s">
-        <v>526</v>
+        <v>284</v>
       </c>
       <c r="D64" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E64" t="s">
-        <v>216</v>
+        <v>498</v>
       </c>
       <c r="F64" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="B65" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="C65" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="D65" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="E65" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="F65" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="B66" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C66" t="s">
-        <v>42</v>
+        <v>559</v>
       </c>
       <c r="D66" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E66" t="s">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="F66" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="B67" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="C67" t="s">
-        <v>544</v>
+        <v>565</v>
       </c>
       <c r="D67" t="s">
-        <v>300</v>
+        <v>229</v>
       </c>
       <c r="E67" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="F67" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
       <c r="B68" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="C68" t="s">
-        <v>273</v>
+        <v>571</v>
       </c>
       <c r="D68" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="F68" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
       <c r="B69" t="s">
-        <v>553</v>
+        <v>575</v>
       </c>
       <c r="C69" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="D69" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E69" t="s">
-        <v>554</v>
+        <v>498</v>
       </c>
       <c r="F69" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B70" t="s">
-        <v>558</v>
+        <v>578</v>
       </c>
       <c r="C70" t="s">
-        <v>250</v>
+        <v>579</v>
       </c>
       <c r="D70" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E70" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="F70" t="s">
-        <v>323</v>
+        <v>581</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>560</v>
+        <v>582</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="B71" t="s">
-        <v>558</v>
+        <v>583</v>
       </c>
       <c r="C71" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="D71" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E71" t="s">
-        <v>559</v>
+        <v>364</v>
       </c>
       <c r="F71" t="s">
-        <v>323</v>
+        <v>237</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>563</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>564</v>
+        <v>586</v>
       </c>
       <c r="B72" t="s">
-        <v>565</v>
+        <v>587</v>
       </c>
       <c r="C72" t="s">
-        <v>250</v>
+        <v>588</v>
       </c>
       <c r="D72" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E72" t="s">
-        <v>448</v>
+        <v>589</v>
       </c>
       <c r="F72" t="s">
-        <v>566</v>
+        <v>216</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>567</v>
+        <v>590</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>568</v>
+        <v>591</v>
       </c>
       <c r="B73" t="s">
-        <v>569</v>
+        <v>592</v>
       </c>
       <c r="C73" t="s">
-        <v>570</v>
+        <v>290</v>
       </c>
       <c r="D73" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E73" t="s">
-        <v>571</v>
+        <v>216</v>
       </c>
       <c r="F73" t="s">
-        <v>572</v>
+        <v>593</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>573</v>
+        <v>594</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>574</v>
+        <v>595</v>
       </c>
       <c r="B74" t="s">
-        <v>569</v>
+        <v>596</v>
       </c>
       <c r="C74" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="D74" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E74" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="F74" t="s">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>577</v>
+        <v>599</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>578</v>
+        <v>600</v>
       </c>
       <c r="B75" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="C75" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
       <c r="D75" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E75" t="s">
-        <v>580</v>
+        <v>602</v>
       </c>
       <c r="F75" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>582</v>
+        <v>604</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="B76" t="s">
-        <v>584</v>
+        <v>606</v>
       </c>
       <c r="C76" t="s">
-        <v>585</v>
+        <v>284</v>
       </c>
       <c r="D76" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E76" t="s">
-        <v>289</v>
+        <v>607</v>
       </c>
       <c r="F76" t="s">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>587</v>
+        <v>609</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>610</v>
+      </c>
+      <c r="B77" t="s">
+        <v>611</v>
+      </c>
+      <c r="C77" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" t="s">
+        <v>481</v>
+      </c>
+      <c r="E77" t="s">
+        <v>612</v>
+      </c>
+      <c r="F77" t="s">
+        <v>319</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>614</v>
+      </c>
+      <c r="B78" t="s">
+        <v>615</v>
+      </c>
+      <c r="C78" t="s">
+        <v>241</v>
+      </c>
+      <c r="D78" t="s">
+        <v>358</v>
+      </c>
+      <c r="E78" t="s">
+        <v>616</v>
+      </c>
+      <c r="F78" t="s">
+        <v>617</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>619</v>
+      </c>
+      <c r="B79" t="s">
+        <v>620</v>
+      </c>
+      <c r="C79" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" t="s">
+        <v>358</v>
+      </c>
+      <c r="E79" t="s">
+        <v>621</v>
+      </c>
+      <c r="F79" t="s">
+        <v>622</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>624</v>
+      </c>
+      <c r="B80" t="s">
+        <v>321</v>
+      </c>
+      <c r="C80" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" t="s">
+        <v>229</v>
+      </c>
+      <c r="E80" t="s">
+        <v>625</v>
+      </c>
+      <c r="F80" t="s">
+        <v>244</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>627</v>
+      </c>
+      <c r="B81" t="s">
+        <v>321</v>
+      </c>
+      <c r="C81" t="s">
+        <v>284</v>
+      </c>
+      <c r="D81" t="s">
+        <v>229</v>
+      </c>
+      <c r="E81" t="s">
+        <v>628</v>
+      </c>
+      <c r="F81" t="s">
+        <v>244</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>630</v>
+      </c>
+      <c r="B82" t="s">
+        <v>631</v>
+      </c>
+      <c r="C82" t="s">
+        <v>632</v>
+      </c>
+      <c r="D82" t="s">
+        <v>229</v>
+      </c>
+      <c r="E82" t="s">
+        <v>633</v>
+      </c>
+      <c r="F82" t="s">
+        <v>634</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>636</v>
+      </c>
+      <c r="B83" t="s">
+        <v>637</v>
+      </c>
+      <c r="C83" t="s">
+        <v>638</v>
+      </c>
+      <c r="D83" t="s">
+        <v>229</v>
+      </c>
+      <c r="E83" t="s">
+        <v>639</v>
+      </c>
+      <c r="F83" t="s">
+        <v>640</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>642</v>
+      </c>
+      <c r="B84" t="s">
+        <v>643</v>
+      </c>
+      <c r="C84" t="s">
+        <v>644</v>
+      </c>
+      <c r="D84" t="s">
+        <v>229</v>
+      </c>
+      <c r="E84" t="s">
+        <v>645</v>
+      </c>
+      <c r="F84" t="s">
+        <v>216</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>647</v>
+      </c>
+      <c r="B85" t="s">
+        <v>648</v>
+      </c>
+      <c r="C85" t="s">
+        <v>284</v>
+      </c>
+      <c r="D85" t="s">
+        <v>229</v>
+      </c>
+      <c r="E85" t="s">
+        <v>347</v>
+      </c>
+      <c r="F85" t="s">
+        <v>216</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>650</v>
+      </c>
+      <c r="B86" t="s">
+        <v>651</v>
+      </c>
+      <c r="C86" t="s">
+        <v>221</v>
+      </c>
+      <c r="D86" t="s">
+        <v>358</v>
+      </c>
+      <c r="E86" t="s">
+        <v>652</v>
+      </c>
+      <c r="F86" t="s">
+        <v>653</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>650</v>
+      </c>
+      <c r="B87" t="s">
+        <v>651</v>
+      </c>
+      <c r="C87" t="s">
+        <v>655</v>
+      </c>
+      <c r="D87" t="s">
+        <v>358</v>
+      </c>
+      <c r="E87" t="s">
+        <v>652</v>
+      </c>
+      <c r="F87" t="s">
+        <v>653</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>657</v>
+      </c>
+      <c r="B88" t="s">
+        <v>658</v>
+      </c>
+      <c r="C88" t="s">
+        <v>140</v>
+      </c>
+      <c r="D88" t="s">
+        <v>229</v>
+      </c>
+      <c r="E88" t="s">
+        <v>659</v>
+      </c>
+      <c r="F88" t="s">
+        <v>660</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>662</v>
+      </c>
+      <c r="B89" t="s">
+        <v>663</v>
+      </c>
+      <c r="C89" t="s">
+        <v>664</v>
+      </c>
+      <c r="D89" t="s">
+        <v>481</v>
+      </c>
+      <c r="E89" t="s">
+        <v>665</v>
+      </c>
+      <c r="F89" t="s">
+        <v>640</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>662</v>
+      </c>
+      <c r="B90" t="s">
+        <v>663</v>
+      </c>
+      <c r="C90" t="s">
+        <v>667</v>
+      </c>
+      <c r="D90" t="s">
+        <v>481</v>
+      </c>
+      <c r="E90" t="s">
+        <v>665</v>
+      </c>
+      <c r="F90" t="s">
+        <v>640</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>669</v>
+      </c>
+      <c r="B91" t="s">
+        <v>670</v>
+      </c>
+      <c r="C91" t="s">
+        <v>221</v>
+      </c>
+      <c r="D91" t="s">
+        <v>229</v>
+      </c>
+      <c r="E91" t="s">
+        <v>671</v>
+      </c>
+      <c r="F91" t="s">
+        <v>672</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>674</v>
+      </c>
+      <c r="B92" t="s">
+        <v>675</v>
+      </c>
+      <c r="C92" t="s">
+        <v>284</v>
+      </c>
+      <c r="D92" t="s">
+        <v>229</v>
+      </c>
+      <c r="E92" t="s">
+        <v>676</v>
+      </c>
+      <c r="F92" t="s">
+        <v>216</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>678</v>
+      </c>
+      <c r="B93" t="s">
+        <v>679</v>
+      </c>
+      <c r="C93" t="s">
+        <v>680</v>
+      </c>
+      <c r="D93" t="s">
+        <v>229</v>
+      </c>
+      <c r="E93" t="s">
+        <v>216</v>
+      </c>
+      <c r="F93" t="s">
+        <v>681</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>683</v>
+      </c>
+      <c r="B94" t="s">
+        <v>684</v>
+      </c>
+      <c r="C94" t="s">
+        <v>685</v>
+      </c>
+      <c r="D94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" t="s">
+        <v>686</v>
+      </c>
+      <c r="F94" t="s">
+        <v>687</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>689</v>
+      </c>
+      <c r="B95" t="s">
+        <v>690</v>
+      </c>
+      <c r="C95" t="s">
+        <v>691</v>
+      </c>
+      <c r="D95" t="s">
+        <v>229</v>
+      </c>
+      <c r="E95" t="s">
+        <v>369</v>
+      </c>
+      <c r="F95" t="s">
+        <v>692</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>694</v>
+      </c>
+      <c r="B96" t="s">
+        <v>695</v>
+      </c>
+      <c r="C96" t="s">
+        <v>306</v>
+      </c>
+      <c r="D96" t="s">
+        <v>229</v>
+      </c>
+      <c r="E96" t="s">
+        <v>696</v>
+      </c>
+      <c r="F96" t="s">
+        <v>697</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>699</v>
+      </c>
+      <c r="B97" t="s">
+        <v>700</v>
+      </c>
+      <c r="C97" t="s">
+        <v>701</v>
+      </c>
+      <c r="D97" t="s">
+        <v>229</v>
+      </c>
+      <c r="E97" t="s">
+        <v>702</v>
+      </c>
+      <c r="F97" t="s">
+        <v>360</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>704</v>
+      </c>
+      <c r="B98" t="s">
+        <v>705</v>
+      </c>
+      <c r="C98" t="s">
+        <v>706</v>
+      </c>
+      <c r="D98" t="s">
+        <v>247</v>
+      </c>
+      <c r="E98" t="s">
+        <v>707</v>
+      </c>
+      <c r="F98" t="s">
+        <v>708</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>710</v>
+      </c>
+      <c r="B99" t="s">
+        <v>711</v>
+      </c>
+      <c r="C99" t="s">
+        <v>42</v>
+      </c>
+      <c r="D99" t="s">
+        <v>229</v>
+      </c>
+      <c r="E99" t="s">
+        <v>712</v>
+      </c>
+      <c r="F99" t="s">
+        <v>713</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>715</v>
+      </c>
+      <c r="B100" t="s">
+        <v>592</v>
+      </c>
+      <c r="C100" t="s">
+        <v>290</v>
+      </c>
+      <c r="D100" t="s">
+        <v>229</v>
+      </c>
+      <c r="E100" t="s">
+        <v>216</v>
+      </c>
+      <c r="F100" t="s">
+        <v>593</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" t="s">
+        <v>363</v>
+      </c>
+      <c r="C101" t="s">
+        <v>284</v>
+      </c>
+      <c r="D101" t="s">
+        <v>247</v>
+      </c>
+      <c r="E101" t="s">
+        <v>717</v>
+      </c>
+      <c r="F101" t="s">
+        <v>718</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>720</v>
+      </c>
+      <c r="B102" t="s">
+        <v>721</v>
+      </c>
+      <c r="C102" t="s">
+        <v>290</v>
+      </c>
+      <c r="D102" t="s">
+        <v>229</v>
+      </c>
+      <c r="E102" t="s">
+        <v>722</v>
+      </c>
+      <c r="F102" t="s">
+        <v>723</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>725</v>
+      </c>
+      <c r="B103" t="s">
+        <v>726</v>
+      </c>
+      <c r="C103" t="s">
+        <v>727</v>
+      </c>
+      <c r="D103" t="s">
+        <v>229</v>
+      </c>
+      <c r="E103" t="s">
+        <v>572</v>
+      </c>
+      <c r="F103" t="s">
+        <v>728</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>730</v>
+      </c>
+      <c r="B104" t="s">
+        <v>731</v>
+      </c>
+      <c r="C104" t="s">
+        <v>680</v>
+      </c>
+      <c r="D104" t="s">
+        <v>247</v>
+      </c>
+      <c r="E104" t="s">
+        <v>732</v>
+      </c>
+      <c r="F104" t="s">
+        <v>319</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>734</v>
+      </c>
+      <c r="B105" t="s">
+        <v>735</v>
+      </c>
+      <c r="C105" t="s">
+        <v>221</v>
+      </c>
+      <c r="D105" t="s">
+        <v>358</v>
+      </c>
+      <c r="E105" t="s">
+        <v>736</v>
+      </c>
+      <c r="F105" t="s">
+        <v>737</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>739</v>
+      </c>
+      <c r="B106" t="s">
+        <v>740</v>
+      </c>
+      <c r="C106" t="s">
+        <v>644</v>
+      </c>
+      <c r="D106" t="s">
+        <v>229</v>
+      </c>
+      <c r="E106" t="s">
+        <v>741</v>
+      </c>
+      <c r="F106" t="s">
+        <v>545</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>743</v>
+      </c>
+      <c r="B107" t="s">
+        <v>744</v>
+      </c>
+      <c r="C107" t="s">
+        <v>745</v>
+      </c>
+      <c r="D107" t="s">
+        <v>481</v>
+      </c>
+      <c r="E107" t="s">
+        <v>746</v>
+      </c>
+      <c r="F107" t="s">
+        <v>747</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>749</v>
+      </c>
+      <c r="B108" t="s">
+        <v>750</v>
+      </c>
+      <c r="C108" t="s">
+        <v>751</v>
+      </c>
+      <c r="D108" t="s">
+        <v>229</v>
+      </c>
+      <c r="E108" t="s">
+        <v>752</v>
+      </c>
+      <c r="F108" t="s">
+        <v>753</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>755</v>
+      </c>
+      <c r="B109" t="s">
+        <v>294</v>
+      </c>
+      <c r="C109" t="s">
+        <v>756</v>
+      </c>
+      <c r="D109" t="s">
+        <v>358</v>
+      </c>
+      <c r="E109" t="s">
+        <v>216</v>
+      </c>
+      <c r="F109" t="s">
+        <v>757</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>759</v>
+      </c>
+      <c r="B110" t="s">
+        <v>760</v>
+      </c>
+      <c r="C110" t="s">
+        <v>761</v>
+      </c>
+      <c r="D110" t="s">
+        <v>229</v>
+      </c>
+      <c r="E110" t="s">
+        <v>762</v>
+      </c>
+      <c r="F110" t="s">
+        <v>763</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>765</v>
+      </c>
+      <c r="B111" t="s">
+        <v>294</v>
+      </c>
+      <c r="C111" t="s">
+        <v>756</v>
+      </c>
+      <c r="D111" t="s">
+        <v>358</v>
+      </c>
+      <c r="E111" t="s">
+        <v>216</v>
+      </c>
+      <c r="F111" t="s">
+        <v>757</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>767</v>
+      </c>
+      <c r="B112" t="s">
+        <v>768</v>
+      </c>
+      <c r="C112" t="s">
+        <v>769</v>
+      </c>
+      <c r="D112" t="s">
+        <v>247</v>
+      </c>
+      <c r="E112" t="s">
+        <v>770</v>
+      </c>
+      <c r="F112" t="s">
+        <v>252</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>772</v>
+      </c>
+      <c r="B113" t="s">
+        <v>773</v>
+      </c>
+      <c r="C113" t="s">
+        <v>42</v>
+      </c>
+      <c r="D113" t="s">
+        <v>229</v>
+      </c>
+      <c r="E113" t="s">
+        <v>774</v>
+      </c>
+      <c r="F113" t="s">
+        <v>775</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>777</v>
+      </c>
+      <c r="B114" t="s">
+        <v>778</v>
+      </c>
+      <c r="C114" t="s">
+        <v>779</v>
+      </c>
+      <c r="D114" t="s">
+        <v>358</v>
+      </c>
+      <c r="E114" t="s">
+        <v>780</v>
+      </c>
+      <c r="F114" t="s">
+        <v>781</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>783</v>
+      </c>
+      <c r="B115" t="s">
+        <v>784</v>
+      </c>
+      <c r="C115" t="s">
+        <v>290</v>
+      </c>
+      <c r="D115" t="s">
+        <v>229</v>
+      </c>
+      <c r="E115" t="s">
+        <v>347</v>
+      </c>
+      <c r="F115" t="s">
+        <v>252</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>786</v>
+      </c>
+      <c r="B116" t="s">
+        <v>787</v>
+      </c>
+      <c r="C116" t="s">
+        <v>788</v>
+      </c>
+      <c r="D116" t="s">
+        <v>229</v>
+      </c>
+      <c r="E116" t="s">
+        <v>789</v>
+      </c>
+      <c r="F116" t="s">
+        <v>431</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>791</v>
+      </c>
+      <c r="B117" t="s">
+        <v>792</v>
+      </c>
+      <c r="C117" t="s">
+        <v>306</v>
+      </c>
+      <c r="D117" t="s">
+        <v>229</v>
+      </c>
+      <c r="E117" t="s">
+        <v>793</v>
+      </c>
+      <c r="F117" t="s">
+        <v>794</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>796</v>
+      </c>
+      <c r="B118" t="s">
+        <v>797</v>
+      </c>
+      <c r="C118" t="s">
+        <v>221</v>
+      </c>
+      <c r="D118" t="s">
+        <v>229</v>
+      </c>
+      <c r="E118" t="s">
+        <v>798</v>
+      </c>
+      <c r="F118" t="s">
+        <v>799</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>801</v>
+      </c>
+      <c r="B119" t="s">
+        <v>802</v>
+      </c>
+      <c r="C119" t="s">
+        <v>221</v>
+      </c>
+      <c r="D119" t="s">
+        <v>229</v>
+      </c>
+      <c r="E119" t="s">
+        <v>803</v>
+      </c>
+      <c r="F119" t="s">
+        <v>407</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>805</v>
+      </c>
+      <c r="B120" t="s">
+        <v>802</v>
+      </c>
+      <c r="C120" t="s">
+        <v>806</v>
+      </c>
+      <c r="D120" t="s">
+        <v>229</v>
+      </c>
+      <c r="E120" t="s">
+        <v>803</v>
+      </c>
+      <c r="F120" t="s">
+        <v>407</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>808</v>
+      </c>
+      <c r="B121" t="s">
+        <v>809</v>
+      </c>
+      <c r="C121" t="s">
+        <v>221</v>
+      </c>
+      <c r="D121" t="s">
+        <v>229</v>
+      </c>
+      <c r="E121" t="s">
+        <v>810</v>
+      </c>
+      <c r="F121" t="s">
+        <v>252</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>812</v>
+      </c>
+      <c r="B122" t="s">
+        <v>813</v>
+      </c>
+      <c r="C122" t="s">
+        <v>221</v>
+      </c>
+      <c r="D122" t="s">
+        <v>229</v>
+      </c>
+      <c r="E122" t="s">
+        <v>607</v>
+      </c>
+      <c r="F122" t="s">
+        <v>737</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>815</v>
+      </c>
+      <c r="B123" t="s">
+        <v>816</v>
+      </c>
+      <c r="C123" t="s">
+        <v>817</v>
+      </c>
+      <c r="D123" t="s">
+        <v>247</v>
+      </c>
+      <c r="E123" t="s">
+        <v>216</v>
+      </c>
+      <c r="F123" t="s">
+        <v>818</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>820</v>
+      </c>
+      <c r="B124" t="s">
+        <v>637</v>
+      </c>
+      <c r="C124" t="s">
+        <v>638</v>
+      </c>
+      <c r="D124" t="s">
+        <v>229</v>
+      </c>
+      <c r="E124" t="s">
+        <v>821</v>
+      </c>
+      <c r="F124" t="s">
+        <v>640</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>823</v>
+      </c>
+      <c r="B125" t="s">
+        <v>735</v>
+      </c>
+      <c r="C125" t="s">
+        <v>221</v>
+      </c>
+      <c r="D125" t="s">
+        <v>358</v>
+      </c>
+      <c r="E125" t="s">
+        <v>736</v>
+      </c>
+      <c r="F125" t="s">
+        <v>737</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>825</v>
+      </c>
+      <c r="B126" t="s">
+        <v>826</v>
+      </c>
+      <c r="C126" t="s">
+        <v>827</v>
+      </c>
+      <c r="D126" t="s">
+        <v>229</v>
+      </c>
+      <c r="E126" t="s">
+        <v>828</v>
+      </c>
+      <c r="F126" t="s">
+        <v>829</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>831</v>
+      </c>
+      <c r="B127" t="s">
+        <v>826</v>
+      </c>
+      <c r="C127" t="s">
+        <v>832</v>
+      </c>
+      <c r="D127" t="s">
+        <v>242</v>
+      </c>
+      <c r="E127" t="s">
+        <v>833</v>
+      </c>
+      <c r="F127" t="s">
+        <v>829</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>835</v>
+      </c>
+      <c r="B128" t="s">
+        <v>836</v>
+      </c>
+      <c r="C128" t="s">
+        <v>221</v>
+      </c>
+      <c r="D128" t="s">
+        <v>229</v>
+      </c>
+      <c r="E128" t="s">
+        <v>837</v>
+      </c>
+      <c r="F128" t="s">
+        <v>838</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>840</v>
+      </c>
+      <c r="B129" t="s">
+        <v>841</v>
+      </c>
+      <c r="C129" t="s">
+        <v>317</v>
+      </c>
+      <c r="D129" t="s">
+        <v>242</v>
+      </c>
+      <c r="E129" t="s">
+        <v>842</v>
+      </c>
+      <c r="F129" t="s">
+        <v>843</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>845</v>
+      </c>
+      <c r="B130" t="s">
+        <v>846</v>
+      </c>
+      <c r="C130" t="s">
+        <v>847</v>
+      </c>
+      <c r="D130" t="s">
+        <v>229</v>
+      </c>
+      <c r="E130" t="s">
+        <v>848</v>
+      </c>
+      <c r="F130" t="s">
+        <v>849</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>851</v>
+      </c>
+      <c r="B131" t="s">
+        <v>852</v>
+      </c>
+      <c r="C131" t="s">
+        <v>221</v>
+      </c>
+      <c r="D131" t="s">
+        <v>229</v>
+      </c>
+      <c r="E131" t="s">
+        <v>853</v>
+      </c>
+      <c r="F131" t="s">
+        <v>854</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>856</v>
+      </c>
+      <c r="B132" t="s">
+        <v>857</v>
+      </c>
+      <c r="C132" t="s">
+        <v>858</v>
+      </c>
+      <c r="D132" t="s">
+        <v>229</v>
+      </c>
+      <c r="E132" t="s">
+        <v>318</v>
+      </c>
+      <c r="F132" t="s">
+        <v>859</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>861</v>
+      </c>
+      <c r="B133" t="s">
+        <v>816</v>
+      </c>
+      <c r="C133" t="s">
+        <v>817</v>
+      </c>
+      <c r="D133" t="s">
+        <v>242</v>
+      </c>
+      <c r="E133" t="s">
+        <v>216</v>
+      </c>
+      <c r="F133" t="s">
+        <v>818</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>863</v>
+      </c>
+      <c r="B134" t="s">
+        <v>864</v>
+      </c>
+      <c r="C134" t="s">
+        <v>464</v>
+      </c>
+      <c r="D134" t="s">
+        <v>229</v>
+      </c>
+      <c r="E134" t="s">
+        <v>865</v>
+      </c>
+      <c r="F134" t="s">
+        <v>866</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>868</v>
+      </c>
+      <c r="B135" t="s">
+        <v>690</v>
+      </c>
+      <c r="C135" t="s">
+        <v>691</v>
+      </c>
+      <c r="D135" t="s">
+        <v>229</v>
+      </c>
+      <c r="E135" t="s">
+        <v>869</v>
+      </c>
+      <c r="F135" t="s">
+        <v>870</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>871</v>
       </c>
     </row>
   </sheetData>
@@ -5137,6 +7874,65 @@
     <hyperlink ref="H74" r:id="rId73"/>
     <hyperlink ref="H75" r:id="rId74"/>
     <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5145,7 +7941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -5184,8 +7980,1138 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2" t="s">
+        <v>875</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>877</v>
+      </c>
+      <c r="B3" t="s">
+        <v>878</v>
+      </c>
+      <c r="C3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3" t="s">
+        <v>879</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>881</v>
+      </c>
+      <c r="B4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F4" t="s">
+        <v>884</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>886</v>
+      </c>
+      <c r="B5" t="s">
+        <v>887</v>
+      </c>
+      <c r="C5" t="s">
+        <v>579</v>
+      </c>
+      <c r="D5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" t="s">
+        <v>884</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>889</v>
+      </c>
+      <c r="B6" t="s">
+        <v>890</v>
+      </c>
+      <c r="C6" t="s">
+        <v>891</v>
+      </c>
+      <c r="D6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" t="s">
+        <v>884</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>893</v>
+      </c>
+      <c r="B7" t="s">
+        <v>894</v>
+      </c>
+      <c r="C7" t="s">
+        <v>895</v>
+      </c>
+      <c r="D7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" t="s">
+        <v>896</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>898</v>
+      </c>
+      <c r="B8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C8" t="s">
+        <v>900</v>
+      </c>
+      <c r="D8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
+        <v>879</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>902</v>
+      </c>
+      <c r="B9" t="s">
+        <v>903</v>
+      </c>
+      <c r="C9" t="s">
+        <v>904</v>
+      </c>
+      <c r="D9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E9" t="s">
+        <v>216</v>
+      </c>
+      <c r="F9" t="s">
+        <v>884</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>906</v>
+      </c>
+      <c r="B10" t="s">
+        <v>899</v>
+      </c>
+      <c r="C10" t="s">
+        <v>900</v>
+      </c>
+      <c r="D10" t="s">
+        <v>216</v>
+      </c>
+      <c r="E10" t="s">
+        <v>216</v>
+      </c>
+      <c r="F10" t="s">
+        <v>879</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>908</v>
+      </c>
+      <c r="B11" t="s">
+        <v>909</v>
+      </c>
+      <c r="C11" t="s">
+        <v>910</v>
+      </c>
+      <c r="D11" t="s">
+        <v>216</v>
+      </c>
+      <c r="E11" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" t="s">
+        <v>884</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>912</v>
+      </c>
+      <c r="B12" t="s">
+        <v>913</v>
+      </c>
+      <c r="C12" t="s">
+        <v>914</v>
+      </c>
+      <c r="D12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" t="s">
+        <v>875</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>916</v>
+      </c>
+      <c r="B13" t="s">
+        <v>917</v>
+      </c>
+      <c r="C13" t="s">
+        <v>918</v>
+      </c>
+      <c r="D13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E13" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" t="s">
+        <v>879</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>920</v>
+      </c>
+      <c r="B14" t="s">
+        <v>921</v>
+      </c>
+      <c r="C14" t="s">
+        <v>922</v>
+      </c>
+      <c r="D14" t="s">
+        <v>216</v>
+      </c>
+      <c r="E14" t="s">
+        <v>216</v>
+      </c>
+      <c r="F14" t="s">
+        <v>884</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>924</v>
+      </c>
+      <c r="B15" t="s">
+        <v>925</v>
+      </c>
+      <c r="C15" t="s">
+        <v>926</v>
+      </c>
+      <c r="D15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E15" t="s">
+        <v>216</v>
+      </c>
+      <c r="F15" t="s">
+        <v>879</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>928</v>
+      </c>
+      <c r="B16" t="s">
+        <v>929</v>
+      </c>
+      <c r="C16" t="s">
+        <v>900</v>
+      </c>
+      <c r="D16" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" t="s">
+        <v>216</v>
+      </c>
+      <c r="F16" t="s">
+        <v>884</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>931</v>
+      </c>
+      <c r="B17" t="s">
+        <v>932</v>
+      </c>
+      <c r="C17" t="s">
+        <v>933</v>
+      </c>
+      <c r="D17" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" t="s">
+        <v>884</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>935</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" t="s">
+        <v>644</v>
+      </c>
+      <c r="D18" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F18" t="s">
+        <v>879</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>937</v>
+      </c>
+      <c r="B19" t="s">
+        <v>938</v>
+      </c>
+      <c r="C19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" t="s">
+        <v>569</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>940</v>
+      </c>
+      <c r="B20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C20" t="s">
+        <v>914</v>
+      </c>
+      <c r="D20" t="s">
+        <v>216</v>
+      </c>
+      <c r="E20" t="s">
+        <v>216</v>
+      </c>
+      <c r="F20" t="s">
+        <v>884</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>942</v>
+      </c>
+      <c r="B21" t="s">
+        <v>943</v>
+      </c>
+      <c r="C21" t="s">
+        <v>914</v>
+      </c>
+      <c r="D21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" t="s">
+        <v>216</v>
+      </c>
+      <c r="F21" t="s">
+        <v>884</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>945</v>
+      </c>
+      <c r="B22" t="s">
+        <v>946</v>
+      </c>
+      <c r="C22" t="s">
+        <v>769</v>
+      </c>
+      <c r="D22" t="s">
+        <v>216</v>
+      </c>
+      <c r="E22" t="s">
+        <v>216</v>
+      </c>
+      <c r="F22" t="s">
+        <v>884</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>948</v>
+      </c>
+      <c r="B23" t="s">
+        <v>949</v>
+      </c>
+      <c r="C23" t="s">
+        <v>950</v>
+      </c>
+      <c r="D23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E23" t="s">
+        <v>216</v>
+      </c>
+      <c r="F23" t="s">
+        <v>884</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>952</v>
+      </c>
+      <c r="B24" t="s">
+        <v>953</v>
+      </c>
+      <c r="C24" t="s">
+        <v>954</v>
+      </c>
+      <c r="D24" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" t="s">
+        <v>216</v>
+      </c>
+      <c r="F24" t="s">
+        <v>884</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>956</v>
+      </c>
+      <c r="B25" t="s">
+        <v>957</v>
+      </c>
+      <c r="C25" t="s">
+        <v>958</v>
+      </c>
+      <c r="D25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E25" t="s">
+        <v>216</v>
+      </c>
+      <c r="F25" t="s">
+        <v>884</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>960</v>
+      </c>
+      <c r="B26" t="s">
+        <v>961</v>
+      </c>
+      <c r="C26" t="s">
+        <v>900</v>
+      </c>
+      <c r="D26" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" t="s">
+        <v>879</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>963</v>
+      </c>
+      <c r="B27" t="s">
+        <v>964</v>
+      </c>
+      <c r="C27" t="s">
+        <v>965</v>
+      </c>
+      <c r="D27" t="s">
+        <v>216</v>
+      </c>
+      <c r="E27" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27" t="s">
+        <v>884</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>967</v>
+      </c>
+      <c r="B28" t="s">
+        <v>968</v>
+      </c>
+      <c r="C28" t="s">
+        <v>969</v>
+      </c>
+      <c r="D28" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" t="s">
+        <v>216</v>
+      </c>
+      <c r="F28" t="s">
+        <v>879</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>967</v>
+      </c>
+      <c r="B29" t="s">
+        <v>971</v>
+      </c>
+      <c r="C29" t="s">
+        <v>972</v>
+      </c>
+      <c r="D29" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" t="s">
+        <v>216</v>
+      </c>
+      <c r="F29" t="s">
+        <v>973</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>975</v>
+      </c>
+      <c r="B30" t="s">
+        <v>976</v>
+      </c>
+      <c r="C30" t="s">
+        <v>904</v>
+      </c>
+      <c r="D30" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" t="s">
+        <v>216</v>
+      </c>
+      <c r="F30" t="s">
+        <v>884</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>978</v>
+      </c>
+      <c r="B31" t="s">
+        <v>979</v>
+      </c>
+      <c r="C31" t="s">
+        <v>980</v>
+      </c>
+      <c r="D31" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" t="s">
+        <v>216</v>
+      </c>
+      <c r="F31" t="s">
+        <v>981</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>983</v>
+      </c>
+      <c r="B32" t="s">
+        <v>984</v>
+      </c>
+      <c r="C32" t="s">
+        <v>985</v>
+      </c>
+      <c r="D32" t="s">
+        <v>216</v>
+      </c>
+      <c r="E32" t="s">
+        <v>216</v>
+      </c>
+      <c r="F32" t="s">
+        <v>884</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>987</v>
+      </c>
+      <c r="B33" t="s">
+        <v>988</v>
+      </c>
+      <c r="C33" t="s">
+        <v>989</v>
+      </c>
+      <c r="D33" t="s">
+        <v>216</v>
+      </c>
+      <c r="E33" t="s">
+        <v>216</v>
+      </c>
+      <c r="F33" t="s">
+        <v>973</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>991</v>
+      </c>
+      <c r="B34" t="s">
+        <v>992</v>
+      </c>
+      <c r="C34" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" t="s">
+        <v>216</v>
+      </c>
+      <c r="E34" t="s">
+        <v>216</v>
+      </c>
+      <c r="F34" t="s">
+        <v>884</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>994</v>
+      </c>
+      <c r="B35" t="s">
+        <v>995</v>
+      </c>
+      <c r="C35" t="s">
+        <v>330</v>
+      </c>
+      <c r="D35" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" t="s">
+        <v>884</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>997</v>
+      </c>
+      <c r="B36" t="s">
+        <v>998</v>
+      </c>
+      <c r="C36" t="s">
+        <v>487</v>
+      </c>
+      <c r="D36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F36" t="s">
+        <v>884</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B37" t="s">
+        <v>925</v>
+      </c>
+      <c r="C37" t="s">
+        <v>926</v>
+      </c>
+      <c r="D37" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" t="s">
+        <v>884</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C38" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38" t="s">
+        <v>216</v>
+      </c>
+      <c r="E38" t="s">
+        <v>216</v>
+      </c>
+      <c r="F38" t="s">
+        <v>879</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C39" t="s">
+        <v>900</v>
+      </c>
+      <c r="D39" t="s">
+        <v>216</v>
+      </c>
+      <c r="E39" t="s">
+        <v>216</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B40" t="s">
+        <v>899</v>
+      </c>
+      <c r="C40" t="s">
+        <v>900</v>
+      </c>
+      <c r="D40" t="s">
+        <v>216</v>
+      </c>
+      <c r="E40" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" t="s">
+        <v>879</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C41" t="s">
+        <v>900</v>
+      </c>
+      <c r="D41" t="s">
+        <v>216</v>
+      </c>
+      <c r="E41" t="s">
+        <v>216</v>
+      </c>
+      <c r="F41" t="s">
+        <v>884</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D42" t="s">
+        <v>216</v>
+      </c>
+      <c r="E42" t="s">
+        <v>216</v>
+      </c>
+      <c r="F42" t="s">
+        <v>884</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" t="s">
+        <v>216</v>
+      </c>
+      <c r="E43" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43" t="s">
+        <v>879</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D44" t="s">
+        <v>216</v>
+      </c>
+      <c r="E44" t="s">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s">
+        <v>973</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D45" t="s">
+        <v>216</v>
+      </c>
+      <c r="E45" t="s">
+        <v>216</v>
+      </c>
+      <c r="F45" t="s">
+        <v>973</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C46" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" t="s">
+        <v>216</v>
+      </c>
+      <c r="E46" t="s">
+        <v>216</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D47" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" t="s">
+        <v>216</v>
+      </c>
+      <c r="F47" t="s">
+        <v>884</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D48" t="s">
+        <v>216</v>
+      </c>
+      <c r="E48" t="s">
+        <v>216</v>
+      </c>
+      <c r="F48" t="s">
+        <v>884</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
